--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>From 197 active orders</t>
+          <t>From 196 active orders</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169 net orders (139 delivered + 28 in progress)</t>
+          <t>168 net orders (139 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -893,7 +893,7 @@
         <v>237652</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.7055837563451777</v>
+        <v>0.7091836734693877</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>25622</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.08121827411167512</v>
+        <v>0.08163265306122448</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>8424</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.02538071065989848</v>
+        <v>0.02551020408163265</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>23614</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.03553299492385787</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1045,7 +1045,7 @@
         <v>92991</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.1421319796954315</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>29884</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.05076142131979695</v>
+        <v>0.05102040816326531</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45520</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.07106598984771574</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>17587</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.02030456852791878</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T198"/>
+  <dimension ref="A1:T197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="119" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -20682,72 +20682,6 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Total Orders</t>
-        </is>
-      </c>
-      <c r="B198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="C198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="S198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="T198" s="5" t="n">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -837,15 +837,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -871,10 +872,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status_Color</t>
         </is>
@@ -897,10 +903,15 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>139 delivered of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Delivered &amp; self fulfilled</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -909,7 +920,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders (Doorstep RTO)</t>
+          <t>Doorstep RTO Denied</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -923,10 +934,15 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>16 doorstep delivery refusals (out of 76 COD orders)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Doorstep delivery denials</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -935,7 +951,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Returned Orders</t>
+          <t>Post-Delivery Customer Returns</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -945,14 +961,19 @@
         <v>8424</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.02551020408163265</v>
+        <v>0.03597122302158273</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>5 customer post-delivery returns (out of 139 delivered)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Delivered then sent back</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
@@ -975,10 +996,15 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>7 canceled of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Order not accepted</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -663,14 +663,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -714,20 +714,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue</t>
+          <t>Full COD Orders</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>63090</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Full COD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>From 40 delivered COD orders</t>
+          <t>55 full COD orders (₹94,928.00)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -744,20 +744,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Avg COD Order Value</t>
+          <t>Partial COD Orders</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1577.25</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>COD net revenue / 40 successful</t>
+          <t>21 Razorpay Partial COD orders (₹53,761.00)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -774,25 +774,25 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue</t>
+          <t>COD Net Revenue</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>174562</v>
+        <v>63090</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Prepaid</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>From 99 delivered Prepaid orders</t>
+          <t>From 40 delivered COD orders</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
@@ -804,23 +804,53 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>174562</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PAY-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Avg Prepaid Order Value</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="3" t="n">
         <v>1763.252525252525</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Prepaid net revenue / 99 successful</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>55 full COD orders (₹94,928.00)</t>
+          <t>55 full COD orders (₹89,768.00)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>21 Razorpay Partial COD orders (₹53,761.00)</t>
+          <t>21 Razorpay Partial COD orders (₹58,921.00)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>94928</v>
+        <v>89768</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.5636363636363636</v>
+        <v>0.5961538461538461</v>
       </c>
     </row>
     <row r="3">
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>53761</v>
+        <v>58921</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>332129</v>
+        <v>334273</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168 net orders (139 delivered + 28 in progress)</t>
+          <t>169 net orders (139 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2389.41726618705</v>
+        <v>2404.841726618705</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>21 Razorpay Partial COD orders (₹58,921.00)</t>
+          <t>21 Razorpay Partial COD orders (₹56,777.00)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>25622</v>
+        <v>23478</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.08163265306122448</v>
+        <v>0.07653061224489796</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>16 doorstep delivery refusals (out of 76 COD orders)</t>
+          <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>17</v>
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>241100</v>
+        <v>243244</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>3</v>
@@ -1603,13 +1603,13 @@
         <v>1</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.05</v>
+        <v>0.05785123966942149</v>
       </c>
     </row>
     <row r="4">
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>58921</v>
+        <v>56777</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3</v>
@@ -1637,16 +1637,16 @@
         <v>3</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +1750,7 @@
         <v>118</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>9</v>
@@ -10394,17 +10394,17 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Partial COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I90" s="5" t="b">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -1448,7 +1448,7 @@
         <v>17</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>4</v>
@@ -1603,13 +1603,13 @@
         <v>1</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.05785123966942149</v>
+        <v>0.04958677685950413</v>
       </c>
     </row>
     <row r="4">
@@ -1640,13 +1640,13 @@
         <v>1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>6</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="I44" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="I48" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -14,7 +14,10 @@
     <sheet name="05_Category_Performance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="06_Payment_Mode_Breakdown" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="07_Monthly_Sales_Trends" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Master_Orders_Dataset" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_Meta_Ads_KPIs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_Meta_Ads_Daywise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_Meta_Ads_Campaigns" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Master_Orders_Dataset" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,203 +660,493 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KPI_ID</t>
+          <t>Campaign_Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Metric_Title</t>
+          <t>Total_Spend_INR</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Primary_Value</t>
+          <t>Impressions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Payment_Type</t>
+          <t>Reach</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Subtext</t>
+          <t>Meta_Results</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Theme_Color</t>
+          <t>Cost_Per_Result_INR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PAY-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Full COD Orders</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Full COD</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>55 full COD orders (₹89,768.00)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
+          <t>JanviAika_Shopping_Ad_Campaign</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>48957.53</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>265314</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>202625</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>425.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PAY-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Partial COD Orders</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Partial COD</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>21 Razorpay Partial COD orders (₹56,777.00)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
+          <t>Anarkali-And-Half-saree-JanviAika_Shopping_Ad_Campaign</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>29884.56</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>61009</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>44018</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1358.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PAY-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>COD Net Revenue</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>63090</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>From 40 delivered COD orders</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
+          <t>JanviAika_Shopping_Ad_Campaign – Lehenga_And_Long_Gowns</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>25939.4</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>96481</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>70875</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>12969.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PAY-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid Net Revenue</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>174562</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>From 99 delivered Prepaid orders</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
+          <t>Hot Campaign for Website Visitors</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20793</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>73478</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>53712</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>433.19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PAY-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Avg Prepaid Order Value</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1763.252525252525</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid net revenue / 99 successful</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
+          <t>Red Anarkali Engagement campaign</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>18856.16</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3628850</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3569798</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>646953</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Lehenga post from Insta</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>18750.33</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1914263</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1827932</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>373958</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Engagement campaign Janviaika Reels</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>9970.719999999999</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1405056</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1341109</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>211730</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Lehenga Set Whatsapp campaign</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8094.79</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>90727</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>20.76</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Retargeting Sales campaign</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2420.1</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>5799</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4531</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>268.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Anarkali Set Whatsapp campaign</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>276.81</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>19019</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>17630</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>46.13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Trendy Green Bridal Couture Whatsapp campaign</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Dark-Pink-Lehenga-Whatsapp-campaign</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Black Half Saree Dress Campaign</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Advantage+ Shopping Campaign March</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Chudidhaar Advantage+ Shopping Campaign</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FB Janviaika Video Campaign_English</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Launch Sales campaign</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Model Engagement Video Campaign</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Post: "Made for summer days, yet wrapped in  elegance 🌿✨ "</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Post: "Who said lehengas are only for brides? ✨ "</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -861,935 +1154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="59" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lifecycle_Stage</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Amount_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Stage_Rate_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Subtext</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status_Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Successful Orders</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>237652</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.7091836734693877</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>139 delivered of 196 total orders</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Delivered &amp; self fulfilled</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Doorstep RTO Denied</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>23478</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.07653061224489796</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Doorstep delivery denials</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Post-Delivery Customer Returns</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>8424</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.03597122302158273</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5 customer post-delivery returns (out of 139 delivered)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Delivered then sent back</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Canceled Orders</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>23614</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.03571428571428571</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7 canceled of 196 total orders</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Order not accepted</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pipeline_Stage</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Amount_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Active_Rate_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Theme_Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total In-Progress</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>92991</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>29884</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.05102040816326531</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Pickup Scheduled</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>45520</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Unfulfilled</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>17587</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.02040816326530612</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Category_Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Revenue_Share_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Delivered_Count</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>In_Transit_Count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unfulfilled_Count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Denied_Count</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Returned_Count</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Canceled_Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ANARKALI</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>76191</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.1954672912781018</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CHUDIDHAR</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>65829</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.1688836780925065</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CO-ORD SET</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2340</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.006003247911049311</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>LEHENGA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>10879</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.02790997180525874</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>LONG GOWN</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>5192</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.01332002698896069</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TOPS</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>250926</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.6437482843281879</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Payment_Mode</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Orders</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Delivered_Count</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>In_Transit_Count</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Pickup_Count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unfulfilled_Count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Denied_Count</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Returned_Count</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Canceled_Count</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Denial_Return_Rate_Pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>89768</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0.5961538461538461</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid (Razorpay)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>243244</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.04958677685950413</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Partial COD</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>56777</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.04347826086956522</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Month_Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Orders</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Gross_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Delivered_Orders</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Denied_Orders</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Returned_Orders</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Canceled_Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>70301</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>266402</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>53086</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20741,4 +20106,3226 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric_Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Payment_Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Theme_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PAY-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Full COD Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Full COD</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>55 full COD orders (₹89,768.00)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PAY-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD Orders</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>21 Razorpay Partial COD orders (₹56,777.00)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PAY-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>COD Net Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>63090</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>From 40 delivered COD orders</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PAY-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>174562</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PAY-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Avg Prepaid Order Value</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1763.252525252525</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid net revenue / 99 successful</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lifecycle_Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Amount_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Stage_Rate_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Successful Orders</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>237652</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.7091836734693877</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>139 delivered of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Delivered &amp; self fulfilled</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Doorstep RTO Denied</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>23478</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.07653061224489796</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Doorstep delivery denials</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Post-Delivery Customer Returns</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>8424</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.03597122302158273</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5 customer post-delivery returns (out of 139 delivered)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Delivered then sent back</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Canceled Orders</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>23614</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7 canceled of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Order not accepted</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pipeline_Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Amount_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Active_Rate_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Theme_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total In-Progress</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>92991</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>29884</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.05102040816326531</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Pickup Scheduled</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>45520</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Unfulfilled</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>17587</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category_Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue_Share_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delivered_Count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>In_Transit_Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unfulfilled_Count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Denied_Count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Returned_Count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Canceled_Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>76191</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.1954672912781018</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>65829</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.1688836780925065</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CO-ORD SET</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2340</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.006003247911049311</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10879</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.02790997180525874</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LONG GOWN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5192</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.01332002698896069</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>250926</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.6437482843281879</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Payment_Mode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Orders</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delivered_Count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>In_Transit_Count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pickup_Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unfulfilled_Count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Denied_Count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Returned_Count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Canceled_Count</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Denial_Return_Rate_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>89768</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.5961538461538461</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>243244</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.04958677685950413</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>56777</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Month_Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Orders</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gross_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delivered_Orders</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Denied_Orders</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Returned_Orders</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Canceled_Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>70301</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>266402</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>53086</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric_Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Theme_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ADS-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Ad Spend</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>183950.69</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>INR ₹</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>June 1 - August 4, 2026</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ADS-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Blended Store ROAS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Gross Revenue ₹389,789.00 / Spend ₹183,950.69</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ADS-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Blended Net ROAS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Net Revenue ₹334,273.00 / Spend ₹183,950.69</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ADS-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Blended Cost Per Acquisition (CPA)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>938.52</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>INR ₹</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Ad Spend ₹183,950.69 / 196 Orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ADS-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Total Audience Reach</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>7223059</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Across 7,575,926 Total Impressions</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Orders_Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sales_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Blended_ROAS</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CPA_INR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>2814.07</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>9962</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1407.04</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>27850</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>25474</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>6790.78</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>11840</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1697.69</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>93142</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>83378</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>7407.9</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>39915</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>673.45</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>179592</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>166065</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>5685.67</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>8584</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2842.84</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>197980</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>181513</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>5226.67</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1306.67</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>103409</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>97468</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4238.28</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>15850</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>847.66</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>94619</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3976.47</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>6550</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>994.12</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>129307</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>121770</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4461.23</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>6660</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1487.08</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>157110</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>146371</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4916.950000000001</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>13690</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>819.49</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>141165</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>135313</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5330.68</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>19070</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>666.34</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>125394</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>116708</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3800.35</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5480</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1900.17</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>105020</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>99787</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>4112.01</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4960</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2056.01</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>108516</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>104715</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>5460</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1081.62</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>137965</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>135234</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4265.29</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>4170</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1421.76</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>140938</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>134815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4573.360000000001</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6158</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>914.67</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>150778</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>144470</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4366.8</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>7248</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1091.7</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>153270</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>146610</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5251.19</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>14008</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>875.2</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>156145</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>148153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4425.94</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3256</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2212.97</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>126165</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>117759</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>4923.72</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10538</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>984.74</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>136227</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>129975</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3752.14</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>6704</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1876.07</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>124333</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>120671</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3909.8</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>5738</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1303.27</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>127317</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>123203</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1032</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>139413</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>130794</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>4558.690000000001</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>8024</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1139.67</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>139141</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>130968</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4608.98</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>6078</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>921.8</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>142747</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>134409</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3708.62</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>4776</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1236.21</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>114921</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>111248</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4671.88</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>25501</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>467.19</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>125570</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>119959</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2731.01</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>11059</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>390.14</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>122955</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>119297</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2487.76</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>4825</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>829.25</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>127272</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>123818</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2503.89</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>500.78</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>118671</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>114126</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2504.42</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>5022</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>626.11</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>123796</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>118722</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2400.14</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>6234</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>800.05</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>121782</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>118434</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3042.28</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>8636</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>507.05</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>144118</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>138473</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>3322.77</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>9805</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>553.79</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>150155</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>143785</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3203.27</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>21468</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>266.94</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>157964</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>147634</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1513.13</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3534</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>504.38</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>90394</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>88635</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1658.34</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>6040</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>414.59</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>57706</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>55086</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2331.12</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>10144</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>86984</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>82745</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1290</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>20835</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>20345</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3424.21</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>16476</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>285.35</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>136298</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>127605</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>121.13</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>4399</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2864.14</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>409.16</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>106921</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>103072</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1017.52</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>10044</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>169.59</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>25339</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>24164</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1699.56</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>81631</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>78423</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1526.93</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1526.93</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>94415</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>91609</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1291.11</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>76255</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>75550</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1092.21</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>82609</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>80995</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1343.2</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>88692</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>86453</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1342.54</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>103489</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>99942</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>1142.68</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>97096</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>94827</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1088.65</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>124560</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>123003</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1289.84</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>167898</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>160149</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>953.3199999999999</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>92242</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>89727</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1178.26</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>111254</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>107443</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1259.9</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>131564</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>128281</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1087.78</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>101813</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>96736</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1135.13</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>109986</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>102732</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1033.66</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>101544</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>96283</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>1248.23</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>125435</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>119265</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>1011.09</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>92146</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>89488</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>1013.36</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>89729</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>86832</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>1106.83</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>129781</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>126564</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>1132.56</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>124016</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>117591</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>1140.34</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>152346</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>145047</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>1113.44</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>155624</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>145187</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>1376.14</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>164696</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>149323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -14,10 +14,7 @@
     <sheet name="05_Category_Performance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="06_Payment_Mode_Breakdown" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="07_Monthly_Sales_Trends" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_Meta_Ads_KPIs" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_Meta_Ads_Daywise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_Meta_Ads_Campaigns" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Master_Orders_Dataset" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Master_Orders_Dataset" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,493 +657,203 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Campaign_Name</t>
+          <t>KPI_ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Total_Spend_INR</t>
+          <t>Metric_Title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Impressions</t>
+          <t>Primary_Value</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Payment_Type</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Meta_Results</t>
+          <t>Subtext</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Cost_Per_Result_INR</t>
+          <t>Theme_Color</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>JanviAika_Shopping_Ad_Campaign</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>48957.53</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>265314</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>202625</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>425.72</v>
+          <t>PAY-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Full COD Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Full COD</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>55 full COD orders (₹89,768.00)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Anarkali-And-Half-saree-JanviAika_Shopping_Ad_Campaign</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>29884.56</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>61009</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>44018</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1358.39</v>
+          <t>PAY-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD Orders</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>21 Razorpay Partial COD orders (₹56,777.00)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>JanviAika_Shopping_Ad_Campaign – Lehenga_And_Long_Gowns</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>25939.4</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>96481</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>70875</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>12969.7</v>
+          <t>PAY-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>COD Net Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>63090</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>From 40 delivered COD orders</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Hot Campaign for Website Visitors</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>20793</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>73478</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>53712</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>433.19</v>
+          <t>PAY-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>174562</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Red Anarkali Engagement campaign</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>18856.16</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>3628850</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>3569798</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>646953</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Lehenga post from Insta</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>18750.33</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1914263</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>1827932</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>373958</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Engagement campaign Janviaika Reels</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>9970.719999999999</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1405056</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>1341109</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>211730</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Lehenga Set Whatsapp campaign</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>8094.79</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>106554</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>90727</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>20.76</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Retargeting Sales campaign</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>2420.1</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>5799</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>4531</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>268.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Anarkali Set Whatsapp campaign</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>276.81</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>19019</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>17630</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>46.13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Trendy Green Bridal Couture Whatsapp campaign</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Dark-Pink-Lehenga-Whatsapp-campaign</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Black Half Saree Dress Campaign</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Advantage+ Shopping Campaign March</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Chudidhaar Advantage+ Shopping Campaign</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>FB Janviaika Video Campaign_English</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Launch Sales campaign</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Model Engagement Video Campaign</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Post: "Made for summer days, yet wrapped in  elegance 🌿✨ "</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Post: "Who said lehengas are only for brides? ✨ "</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0</v>
+          <t>PAY-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Avg Prepaid Order Value</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1763.252525252525</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid net revenue / 99 successful</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +861,935 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lifecycle_Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Amount_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Stage_Rate_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Successful Orders</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>237652</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.7091836734693877</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>139 delivered of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Delivered &amp; self fulfilled</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Doorstep RTO Denied</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>23478</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.07653061224489796</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Doorstep delivery denials</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Post-Delivery Customer Returns</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>8424</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.03597122302158273</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5 customer post-delivery returns (out of 139 delivered)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Delivered then sent back</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Canceled Orders</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>23614</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7 canceled of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Order not accepted</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pipeline_Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Amount_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Active_Rate_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Theme_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total In-Progress</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>92991</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>29884</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.05102040816326531</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Pickup Scheduled</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>45520</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Unfulfilled</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>17587</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category_Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue_Share_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delivered_Count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>In_Transit_Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unfulfilled_Count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Denied_Count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Returned_Count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Canceled_Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>76191</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.1954672912781018</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>65829</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.1688836780925065</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CO-ORD SET</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2340</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.006003247911049311</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10879</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.02790997180525874</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LONG GOWN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5192</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.01332002698896069</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>250926</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.6437482843281879</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Payment_Mode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Orders</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delivered_Count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>In_Transit_Count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pickup_Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unfulfilled_Count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Denied_Count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Returned_Count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Canceled_Count</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Denial_Return_Rate_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>89768</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.5961538461538461</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>243244</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.04958677685950413</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>56777</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Month_Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Orders</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gross_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delivered_Orders</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Denied_Orders</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Returned_Orders</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Canceled_Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>70301</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>266402</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>53086</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3658,7 +4293,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7786,7 +8421,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -20101,3228 +20736,6 @@
         <is>
           <t>TOPS</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KPI_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Metric_Title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Primary_Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Payment_Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Subtext</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Theme_Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PAY-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Full COD Orders</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Full COD</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>55 full COD orders (₹89,768.00)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>PAY-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Partial COD Orders</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Partial COD</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>21 Razorpay Partial COD orders (₹56,777.00)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PAY-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>COD Net Revenue</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>63090</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>From 40 delivered COD orders</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>PAY-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid Net Revenue</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>174562</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>From 99 delivered Prepaid orders</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>PAY-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Avg Prepaid Order Value</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1763.252525252525</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid net revenue / 99 successful</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="59" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lifecycle_Stage</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Amount_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Stage_Rate_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Subtext</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status_Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Successful Orders</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>237652</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.7091836734693877</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>139 delivered of 196 total orders</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Delivered &amp; self fulfilled</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Doorstep RTO Denied</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>23478</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.07653061224489796</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Doorstep delivery denials</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Post-Delivery Customer Returns</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>8424</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.03597122302158273</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5 customer post-delivery returns (out of 139 delivered)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Delivered then sent back</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Canceled Orders</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>23614</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.03571428571428571</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7 canceled of 196 total orders</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Order not accepted</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pipeline_Stage</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Amount_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Active_Rate_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Theme_Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total In-Progress</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>92991</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>29884</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.05102040816326531</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Pickup Scheduled</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>45520</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Unfulfilled</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>17587</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.02040816326530612</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Category_Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Order_Count</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Revenue_Share_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Delivered_Count</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>In_Transit_Count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unfulfilled_Count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Denied_Count</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Returned_Count</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Canceled_Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ANARKALI</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>76191</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.1954672912781018</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CHUDIDHAR</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>65829</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.1688836780925065</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CO-ORD SET</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2340</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.006003247911049311</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>LEHENGA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>10879</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.02790997180525874</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>LONG GOWN</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>5192</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.01332002698896069</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TOPS</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>250926</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.6437482843281879</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Payment_Mode</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Orders</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Delivered_Count</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>In_Transit_Count</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Pickup_Count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unfulfilled_Count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Denied_Count</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Returned_Count</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Canceled_Count</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Denial_Return_Rate_Pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>89768</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0.5961538461538461</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid (Razorpay)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>243244</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.04958677685950413</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Partial COD</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>56777</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.04347826086956522</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Month_Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Orders</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Gross_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Delivered_Orders</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Denied_Orders</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Returned_Orders</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Canceled_Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>70301</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>266402</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>53086</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KPI_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Metric_Title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Primary_Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Subtext</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Theme_Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ADS-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Total Meta Ad Spend</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>183950.69</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>INR ₹</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>June 1 - August 4, 2026</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ADS-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Blended Store ROAS</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Gross Revenue ₹389,789.00 / Spend ₹183,950.69</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ADS-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Blended Net ROAS</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Net Revenue ₹334,273.00 / Spend ₹183,950.69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ADS-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Blended Cost Per Acquisition (CPA)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>938.52</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>INR ₹</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Ad Spend ₹183,950.69 / 196 Orders</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ADS-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Total Audience Reach</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>7223059</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Across 7,575,926 Total Impressions</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ad_Spend_INR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Orders_Count</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sales_Revenue_INR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Blended_ROAS</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CPA_INR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>2814.07</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>9962</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1407.04</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>27850</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>25474</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>6790.78</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>11840</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1697.69</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>93142</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>83378</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>7407.9</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>39915</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>673.45</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>179592</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>166065</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>5685.67</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>8584</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>2842.84</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>197980</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>181513</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>5226.67</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1306.67</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>103409</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>97468</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>4238.28</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>15850</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>847.66</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>94619</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>3976.47</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>6550</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>994.12</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>129307</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>121770</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>4461.23</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>6660</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1487.08</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>157110</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>146371</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>4916.950000000001</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>13690</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>819.49</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>141165</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>135313</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>5330.68</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>19070</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>666.34</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>125394</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>116708</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>3800.35</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>5480</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1900.17</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>105020</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>99787</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>4112.01</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>4960</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>2056.01</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>108516</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>104715</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>4326.5</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>5460</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1081.62</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>137965</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>135234</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>4265.29</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>4170</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>1421.76</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>140938</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>134815</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>4573.360000000001</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>6158</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>914.67</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>150778</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>144470</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>4366.8</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>7248</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1091.7</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>153270</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>146610</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>5251.19</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>14008</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>875.2</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>156145</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>148153</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>4425.94</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>3256</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>2212.97</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>126165</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>117759</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>4923.72</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>10538</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>984.74</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>136227</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>129975</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>3752.14</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>6704</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>1876.07</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>124333</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>120671</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>3909.8</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>5738</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>1303.27</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>127317</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>123203</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>4519.55</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>1032</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>4519.55</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>139413</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>130794</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>4558.690000000001</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>8024</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>1139.67</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>139141</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>130968</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>4608.98</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>6078</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>921.8</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>142747</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>134409</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>3708.62</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>4776</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>1236.21</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>114921</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>111248</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>4671.88</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>25501</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>467.19</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>125570</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>119959</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>2731.01</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>11059</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>390.14</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>122955</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>119297</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>2487.76</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>4825</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>829.25</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>127272</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>123818</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>2503.89</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>7068</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>500.78</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>118671</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>114126</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>2504.42</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>5022</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>626.11</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>123796</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>118722</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>2400.14</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>6234</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>800.05</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>121782</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>118434</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>3042.28</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>8636</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>507.05</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>144118</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>138473</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>3322.77</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>9805</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>553.79</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>150155</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>143785</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>3203.27</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>21468</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>266.94</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>157964</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>147634</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>1513.13</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>3534</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>504.38</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>90394</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>88635</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>1658.34</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>6040</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>414.59</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>57706</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>55086</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>2331.12</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>10144</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>388.52</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>86984</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>82745</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>595.28</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>1290</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>595.28</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>20835</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>20345</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>3424.21</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>16476</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>285.35</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>136298</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>127605</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>121.13</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>4399</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>4219</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>2864.14</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>7980</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>409.16</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>106921</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>103072</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>1017.52</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>10044</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>169.59</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>25339</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>24164</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>1699.56</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>81631</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>78423</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>1526.93</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>1112</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1526.93</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>94415</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>91609</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>1291.11</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>76255</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>75550</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>1092.21</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>82609</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>80995</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>1343.2</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>88692</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>86453</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>1342.54</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>103489</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>99942</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>1142.68</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>97096</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>94827</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>1088.65</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>124560</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>123003</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>1289.84</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>167898</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>160149</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>953.3199999999999</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>92242</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>89727</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>1178.26</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>111254</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>107443</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>1259.9</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>131564</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>128281</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>1087.78</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>101813</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>96736</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>1135.13</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>109986</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>102732</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>1033.66</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>101544</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>96283</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>1248.23</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>125435</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>119265</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>1011.09</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>92146</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>89488</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>1013.36</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>89729</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>86832</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>1106.83</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>129781</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>126564</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>1132.56</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>124016</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>117591</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>1140.34</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>152346</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>145047</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>1113.44</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>155624</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>145187</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>1376.14</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>164696</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>149323</v>
       </c>
     </row>
   </sheetData>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_Executive_KPIs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_Payment_KPIs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Lifecycle_Metrics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_In_Progress_Pipeline" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_Category_Performance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_Payment_Mode_Breakdown" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_Monthly_Sales_Trends" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Master_Orders_Dataset" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="00_All_Card_Details_With_Subtext" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Executive_KPIs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Payment_KPIs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_Lifecycle_Metrics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_In_Progress_Pipeline" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Category_Performance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_Payment_Mode_Breakdown" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_Monthly_Sales_Trends" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Master_Orders_Dataset" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="67" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="108" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Card_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Card_Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Display_Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext_Line_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext_Line_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Full_Card_Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CARD-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Active Shopify Orders</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>196 total store orders</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Total Orders: 196 | Subtext: Active Shopify Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CARD-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>389789</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>₹389,789.00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>From 196 active orders</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Gross total sales</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Total Revenue: ₹389,789.00 | Subtext: From 196 active orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CARD-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Net Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>334273</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>₹334,273.00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>169 net orders (86.2% of total: 139 delivered + 28 in progress)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Excludes RTO &amp; Canceled</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Net Revenue: ₹334,273.00 | Subtext: 169 net orders (139 delivered + 28 in progress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CARD-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Average Order Value (AOV)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2404.841726618705</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>~ ₹2,404.84</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Net revenue / 139 successful</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Net AOV across 139 delivered</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Average Order Value: ~ ₹2,404.84 | Subtext: Net revenue / 139 successful</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CARD-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>COD Net Revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>63090</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>₹63,090.00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>From 40 delivered COD orders</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Net delivered COD revenue</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>COD Net Revenue: ₹63,090.00 | Subtext: From 40 delivered COD orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CARD-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Avg COD Order Value</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1577.25</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>~ ₹1,577.25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>COD net revenue / 40 successful</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Average value of 40 delivered COD orders</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Avg COD Order Value: ~ ₹1,577.25 | Subtext: COD net revenue / 40 successful</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CARD-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>174562</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>₹174,562.00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Net delivered prepaid revenue</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid Net Revenue: ₹174,562.00 | Subtext: From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CARD-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Avg Prepaid Order Value</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1763.252525252525</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>~ ₹1,763.25</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid net revenue / 99 successful</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Average value of 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Avg Prepaid Order Value: ~ ₹1,763.25 | Subtext: Prepaid net revenue / 99 successful</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CARD-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Successful Orders</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139 delivered of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Count 139 | Successful Revenue ₹237,652.00 | Successful Rate 70.9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Successful Orders: 139 | Revenue: ₹237,652.00 | Rate: 70.9% | Subtext: 139 delivered of 196 total orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CARD-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Denied Orders (Doorstep RTO)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15 denied of 196 total orders (19.7% of 76 COD)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Count 15 | Total Amount ₹23,478.00 | Denied Rate 7.7%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Denied Orders: 15 | Amount: ₹23,478.00 | Rate: 7.7% | Subtext: 15 doorstep delivery refusals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CARD-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Returned Orders</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5 customer post-delivery returns of 139 delivered</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Count 5 | Total Refunded ₹8,424.00 | Return Rate 3.6%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Returned Orders: 5 | Refunded: ₹8,424.00 | Rate: 3.6% | Subtext: 5 customer post-delivery returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CARD-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Canceled Orders</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7 canceled of 196 total orders</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Count 7 | Total Amount ₹23,614.00 | Canceled Rate 3.6%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Canceled Orders: 7 | Amount: ₹23,614.00 | Rate: 3.6% | Subtext: 7 canceled of 196 total orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CARD-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Total In-Progress Pipeline</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28 orders awaiting delivery of 196</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Count 28 | Total Amount ₹92,991.00 | Active Rate 14.3%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Total In-Progress: 28 | Amount: ₹92,991.00 | Rate: 14.3% | Subtext: 28 orders awaiting delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CARD-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10 orders on the way of 196</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Count 10 | Total Amount ₹29,884.00 | Transit Rate 5.1%</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>In Transit: 10 | Amount: ₹29,884.00 | Subtext: 10 orders on the way</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CARD-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Pickup Scheduled</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14 orders ready for pickup of 196</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Count 14 | Total Amount ₹45,520.00 | Pickup Rate 7.1%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Pickup Scheduled: 14 | Amount: ₹45,520.00 | Subtext: 14 orders ready for pickup</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CARD-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Unfulfilled</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4 orders pending shipment of 196</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Count 4 | Total Amount ₹17,587.00 | Unfulfilled Rate 2.0%</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Unfulfilled: 4 | Amount: ₹17,587.00 | Subtext: 4 orders pending shipment</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -479,8 +1100,9 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="51" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -511,10 +1133,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Full_Card_Display</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Progress_Pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Theme_Color</t>
         </is>
@@ -544,10 +1171,15 @@
           <t>Active Shopify Orders</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Total Orders: 196 (Active Shopify Orders)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
@@ -577,10 +1209,15 @@
           <t>From 196 active orders</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Total Revenue: ₹389,789.00 (From 196 active orders)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -610,10 +1247,15 @@
           <t>169 net orders (139 delivered + 28 in progress)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Net Revenue: ₹334,273.00 (169 net orders)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -643,10 +1285,15 @@
           <t>Net revenue / 139 successful</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>AOV: ₹2,404.84 (Net revenue / 139 successful)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
@@ -657,7 +1304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -861,7 +1508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1045,7 +1692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1177,7 +1824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1459,7 +2106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1654,7 +2301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1789,7 +2436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_All_Card_Details_With_Subtext" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="00_Card_Details_With_Subtext" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="01_Executive_KPIs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="02_Payment_KPIs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="03_Lifecycle_Metrics" sheetId="4" state="visible" r:id="rId4"/>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -1698,14 +1698,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1731,6 +1732,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Theme_Color</t>
         </is>
       </c>
@@ -1752,6 +1758,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>28 orders awaiting delivery of 196</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Blue</t>
         </is>
       </c>
@@ -1773,6 +1784,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>10 orders on the way of 196</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Blue</t>
         </is>
       </c>
@@ -1794,6 +1810,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>14 orders ready for pickup of 196</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Purple</t>
         </is>
       </c>
@@ -1814,6 +1835,11 @@
         <v>0.02040816326530612</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4 orders pending shipment of 196</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -16,6 +16,10 @@
     <sheet name="06_Payment_Mode_Breakdown" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="07_Monthly_Sales_Trends" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Master_Orders_Dataset" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="08_Meta_Ads_KPIs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="09_Meta_Ads_Category_Perf" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10_Meta_Ads_Source_Breakdown" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11_Meta_Ads_Campaign_Details" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1078,6 +1082,1348 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Unfulfilled: 4 | Amount: ₹17,587.00 | Subtext: 4 orders pending shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CARD-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Ad Spend</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>226394.41</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>₹2,26,394.41</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Ads spend (Apr 01 - Aug 04)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Includes Advantage+, Reels, Insta &amp; WA Ads</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Ad Spend: ₹2,26,394.41 | Subtext: Total Meta Ads spend (Apr 01 - Aug 04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CARD-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Impressions</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>13862586</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13.86M</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13.86M ad impressions served across Meta</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13,862,586 total impressions</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Impressions: 13.86M | Subtext: 13.86M ad impressions served</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CARD-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Reach</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>13156590</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13.15M</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13.15M unique users reached across Meta</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13,156,590 total unique reach</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Reach: 13.15M | Subtext: 13.15M unique users reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CARD-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Cost Per Purchase (CPA)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1155.07</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>₹1,155.07</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ad spend / 196 pixel purchase conversions</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Average cost to acquire 1 purchase</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Cost Per Purchase (CPA): ₹1,155.07 | Subtext: Ad spend / 196 pixel purchase conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CARD-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Gross ROAS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1.72x</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1.72x Gross Return on Ad Spend</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Gross ROAS: 1.72x | Subtext: Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CARD-22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Net ROAS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1.48x</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Net Sales (₹3,34,273) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1.48x Net Return on Ad Spend</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Net ROAS: 1.48x | Subtext: Net Sales (₹3,34,273) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric_Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Theme_Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>META-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Ad Spend</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>226394.41</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>INR ₹</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Ads spend (Apr 01 - Aug 04)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>META-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Impressions</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>13862586</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Views</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>13.86M ad impressions served</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>META-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Total Meta Reach</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>13156590</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13.16M unique users reached</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>META-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Cost Per Purchase (CPA)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1155.073520408163</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>INR ₹</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Ad spend / 196 pixel purchase conversions</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>META-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Gross ROAS</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.721725372989554</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Gross sales (₹389,789) / Ad spend (₹226,394)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>META-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Net ROAS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.476507304221866</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Net sales (₹334,273) / Ad spend (₹226,394)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category_Tag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Amount spent (INR)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spend_Share_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>20850.6</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>3990043</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>3924326</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.09209856374103935</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI &amp; HALF SAREE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>29884.56</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>61009</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>44018</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.1320021991709071</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SHOPPING CAMPAIGNS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>55242.89</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>668157</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>580140</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.2440117227276062</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA &amp; LONG GOWNS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>65240.58</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4317747</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4031999</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.2881722212134125</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>REELS &amp; BRAND ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>31962.68</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>4746353</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4517864</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.14118140107788</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RETARGETING &amp; AUDIENCE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>23213.1</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>79277</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>58243</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.1025338920691549</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ad_Source_Tag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Amount spent (INR)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Channel_Share_Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FACEBOOK ADS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>19908.2</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>2985964</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>2837488</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.08793591679229182</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>INSTAGRAM ADS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>40719.68</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>5837786</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5520031</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.1798616847474281</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>131633.38</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>4796574</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4601633</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.5814338790432149</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RETARGETING ADS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>23213.1</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>79277</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>58243</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.1025338920691549</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP ADS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10920.05</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>162985</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>139195</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.04823462734791022</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Amount spent (INR)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category_Tag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ad_Source_Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Advantage+ Shopping Campaign March</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SHOPPING CAMPAIGNS</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Anarkali Set Whatsapp campaign</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>276.81</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>19019</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>17630</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Anarkali-And-Half-saree-JanviAika_Shopping_Ad_Campaign</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>29884.56</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>61009</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>44018</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI &amp; HALF SAREE</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Black Half Saree Dress Campaign</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6278.1</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>402746</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>377419</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SHOPPING CAMPAIGNS</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Chudidhaar Advantage+ Shopping Campaign</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Dark-Pink-Lehenga-Whatsapp-campaign</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA &amp; LONG GOWNS</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Engagement campaign Janviaika Reels</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>9970.719999999999</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1405056</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1341109</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>REELS &amp; BRAND ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>INSTAGRAM ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FB Janviaika Video Campaign_English</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>19908.2</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2985964</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2837488</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>REELS &amp; BRAND ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>FACEBOOK ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Hot Campaign for Website Visitors</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>20793</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>73478</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>53712</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>RETARGETING &amp; AUDIENCE</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>RETARGETING ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>JanviAika_Shopping_Ad_Campaign</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>48957.53</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>265314</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>202625</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SHOPPING CAMPAIGNS</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>JanviAika_Shopping_Ad_Campaign – Lehenga_And_Long_Gowns</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>25939.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>96481</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>70875</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA &amp; LONG GOWNS</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Launch Sales campaign</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SHOPPING CAMPAIGNS</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Lehenga Set Whatsapp campaign</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>10635.95</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>143863</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>121463</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA &amp; LONG GOWNS</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Lehenga post from Insta</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>27538.9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3910483</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3672890</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA &amp; LONG GOWNS</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>INSTAGRAM ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Model Engagement Video Campaign</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>REELS &amp; BRAND ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Post: "Made for summer days, yet wrapped in  elegance 🌿✨ "</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2083.76</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>355333</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>339267</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>REELS &amp; BRAND ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>INSTAGRAM ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Post: "Who said lehengas are only for brides? ✨ "</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1126.3</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>166914</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>166765</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>LEHENGA &amp; LONG GOWNS</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>INSTAGRAM ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Red Anarkali Engagement campaign</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>20573.79</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>3971024</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3906696</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>META ADVANTAGE+ / SHOPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Retargeting Sales campaign</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2420.1</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>5799</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>4531</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>RETARGETING &amp; AUDIENCE</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>RETARGETING ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Trendy Green Bridal Couture Whatsapp campaign</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SHOPPING CAMPAIGNS</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP ADS</t>
         </is>
       </c>
     </row>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -480,7 +480,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="67" customWidth="1" min="5" max="5"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Total Orders</t>
+          <t>Total Orders (Active Shopify Orders)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -568,7 +568,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Total Revenue (From 196 active orders)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue</t>
+          <t>Net Revenue (169 net orders: 139 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value (AOV)</t>
+          <t>Average Order Value (AOV) (Net revenue / 139 successful)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue</t>
+          <t>COD Net Revenue (From 40 delivered COD orders)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Avg COD Order Value</t>
+          <t>Avg COD Order Value (COD net / 40 successful)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue</t>
+          <t>Prepaid Net Revenue (From 99 delivered Prepaid orders)</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value</t>
+          <t>Avg Prepaid Order Value (Prepaid net / 99 successful)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders</t>
+          <t>Successful Orders (139 delivered of 196 total orders)</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders (Doorstep RTO)</t>
+          <t>Denied Orders (Doorstep RTO) (15 refused of 76 COD orders)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Returned Orders</t>
+          <t>Returned Orders (5 customer returns of 139 delivered)</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders</t>
+          <t>Canceled Orders (7 canceled of 196 total orders)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress Pipeline</t>
+          <t>Total In-Progress Pipeline (28 orders awaiting delivery)</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
+          <t>In Transit (10 orders on the way of 196)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled</t>
+          <t>Pickup Scheduled (14 orders ready for pickup of 196)</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled</t>
+          <t>Unfulfilled (4 orders pending shipment of 196)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Ad Spend</t>
+          <t>Total Meta Ad Spend (Apr 01 - Aug 04)</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Impressions</t>
+          <t>Total Meta Impressions (13.86M ad impressions)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Reach</t>
+          <t>Total Meta Reach (13.15M unique users reached)</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cost Per Purchase (CPA)</t>
+          <t>Cost Per Purchase (CPA) (Ad spend / 196 conversions)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Gross ROAS</t>
+          <t>Gross ROAS (Gross Sales ₹3,89,789 / Spend ₹2,26,394)</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Net ROAS</t>
+          <t>Net ROAS (Net Sales ₹3,34,273 / Spend ₹2,26,394)</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -2442,7 +2442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="51" customWidth="1" min="5" max="5"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Total Orders</t>
+          <t>Total Orders (Active Shopify Orders)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Total Revenue (From 196 active orders)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue</t>
+          <t>Net Revenue (169 net orders: 139 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value (AOV)</t>
+          <t>Average Order Value (AOV) (Net revenue / 139 successful)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2660,7 +2660,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Full COD Orders</t>
+          <t>Full COD Orders (Pre-July 24 100% Cash on Delivery)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>55 full COD orders (₹89,768.00)</t>
+          <t>52 full COD orders (₹89,768.00)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Partial COD Orders</t>
+          <t>Partial COD Orders (July 24+ Razorpay Advance Paid)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>21 Razorpay Partial COD orders (₹56,777.00)</t>
+          <t>23 Razorpay Partial COD orders (₹56,777.00)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue</t>
+          <t>COD Net Revenue (From 40 delivered COD orders)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue</t>
+          <t>Prepaid Net Revenue (From 99 delivered Prepaid orders)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value</t>
+          <t>Avg Prepaid Order Value (Prepaid net / 99 successful)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2863,7 +2863,7 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -2912,7 +2912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders</t>
+          <t>Successful Orders (139 delivered of 196 total orders)</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
@@ -2943,7 +2943,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Doorstep RTO Denied</t>
+          <t>Doorstep RTO Denied (15 refused of 76 COD orders)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -2974,7 +2974,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Post-Delivery Customer Returns</t>
+          <t>Post-Delivery Customer Returns (5 customer returns of 139 delivered)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -3005,7 +3005,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders</t>
+          <t>Canceled Orders (7 canceled of 196 total orders)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -3047,7 +3047,7 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -3090,7 +3090,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress</t>
+          <t>Total In-Progress (28 orders awaiting delivery)</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
@@ -3116,7 +3116,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
+          <t>In Transit (10 orders on the way of 196)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -3142,7 +3142,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled</t>
+          <t>Pickup Scheduled (14 orders ready for pickup of 196)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -3168,7 +3168,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled</t>
+          <t>Unfulfilled (4 orders pending shipment of 196)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -480,9 +480,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
     <col width="67" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="108" customWidth="1" min="7" max="7"/>
@@ -533,15 +533,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Total Orders (Active Shopify Orders)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>196</v>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>196 (Active Shopify Orders)</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>196 (Active Shopify Orders)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -568,15 +570,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Total Revenue (From 196 active orders)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>389789</v>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>₹389,789.00 (From 196 active orders)</t>
+        </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>₹389,789.00</t>
+          <t>₹389,789.00 (From 196 active orders)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -603,15 +607,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue (169 net orders: 139 delivered + 28 in progress)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>334273</v>
+          <t>Net Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>₹334,273.00 (169 net orders: 139 delivered + 28 in progress)</t>
+        </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>₹334,273.00</t>
+          <t>₹334,273.00 (169 net orders)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -638,15 +644,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value (AOV) (Net revenue / 139 successful)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>2404.841726618705</v>
+          <t>Average Order Value (AOV)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>₹2,404.84 (Net revenue / 139 successful)</t>
+        </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>~ ₹2,404.84</t>
+          <t>~ ₹2,404.84 (Net revenue / 139 successful)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -673,15 +681,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue (From 40 delivered COD orders)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>63090</v>
+          <t>COD Net Revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>₹63,090.00 (From 40 delivered COD orders)</t>
+        </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>₹63,090.00</t>
+          <t>₹63,090.00 (From 40 delivered COD orders)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -708,15 +718,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Avg COD Order Value (COD net / 40 successful)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1577.25</v>
+          <t>Avg COD Order Value</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>₹1,577.25 (COD net / 40 successful)</t>
+        </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>~ ₹1,577.25</t>
+          <t>~ ₹1,577.25 (COD net / 40 successful)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -743,15 +755,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue (From 99 delivered Prepaid orders)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>174562</v>
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
+        </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>₹174,562.00</t>
+          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -778,15 +792,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value (Prepaid net / 99 successful)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1763.252525252525</v>
+          <t>Avg Prepaid Order Value</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>₹1,763.25 (Prepaid net / 99 successful)</t>
+        </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>~ ₹1,763.25</t>
+          <t>~ ₹1,763.25 (Prepaid net / 99 successful)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -813,15 +829,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders (139 delivered of 196 total orders)</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>139</v>
+          <t>Successful Orders</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>139 (139 delivered of 196 total orders)</t>
+        </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>139 (139 delivered of 196 total orders)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -848,15 +866,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders (Doorstep RTO) (15 refused of 76 COD orders)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>15</v>
+          <t>Denied Orders (Doorstep RTO)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15 (15 refused of 76 COD orders)</t>
+        </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15 (15 refused of 76 COD orders)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,15 +903,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Returned Orders (5 customer returns of 139 delivered)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>5</v>
+          <t>Returned Orders</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5 (5 customer returns of 139 delivered)</t>
+        </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (5 customer returns of 139 delivered)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -918,15 +940,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders (7 canceled of 196 total orders)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>7</v>
+          <t>Canceled Orders</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7 (7 canceled of 196 total orders)</t>
+        </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (7 canceled of 196 total orders)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -953,15 +977,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress Pipeline (28 orders awaiting delivery)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>28</v>
+          <t>Total In-Progress Pipeline</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>28 (28 orders awaiting delivery)</t>
+        </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>28 (28 orders awaiting delivery)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -988,15 +1014,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>In Transit (10 orders on the way of 196)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>10</v>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10 (10 orders on the way of 196)</t>
+        </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (10 orders on the way of 196)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1023,15 +1051,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled (14 orders ready for pickup of 196)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>14</v>
+          <t>Pickup Scheduled</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>14 (14 orders ready for pickup of 196)</t>
+        </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 (14 orders ready for pickup of 196)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1058,15 +1088,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled (4 orders pending shipment of 196)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>4</v>
+          <t>Unfulfilled</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4 (4 orders pending shipment of 196)</t>
+        </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 (4 orders pending shipment of 196)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1093,15 +1125,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Ad Spend (Apr 01 - Aug 04)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>226394.41</v>
+          <t>Total Meta Ad Spend</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>₹2,26,394.41 (Apr 01 - Aug 04)</t>
+        </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>₹2,26,394.41</t>
+          <t>₹2,26,394.41 (Apr 01 - Aug 04)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1128,15 +1162,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Impressions (13.86M ad impressions)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>13862586</v>
+          <t>Total Meta Impressions</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>13.86M (13.86M ad impressions)</t>
+        </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13.86M</t>
+          <t>13.86M (13.86M ad impressions)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1163,15 +1199,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Reach (13.15M unique users reached)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>13156590</v>
+          <t>Total Meta Reach</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>13.15M (13.15M unique reach)</t>
+        </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13.15M</t>
+          <t>13.15M (13.15M unique reach)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1198,15 +1236,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cost Per Purchase (CPA) (Ad spend / 196 conversions)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1155.07</v>
+          <t>Cost Per Purchase (CPA)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>₹1,155.07 (Ad spend / 196 conversions)</t>
+        </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>₹1,155.07</t>
+          <t>₹1,155.07 (Ad spend / 196 conversions)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1233,15 +1273,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Gross ROAS (Gross Sales ₹3,89,789 / Spend ₹2,26,394)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>1.72</v>
+          <t>Gross ROAS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1.72x (Gross Sales ₹3,89,789 / Spend ₹2,26,394)</t>
+        </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1.72x</t>
+          <t>1.72x (Gross Sales ₹3,89,789 / Spend ₹2,26,394)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1268,15 +1310,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Net ROAS (Net Sales ₹3,34,273 / Spend ₹2,26,394)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1.48</v>
+          <t>Net ROAS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1.48x (Net Sales ₹3,34,273 / Spend ₹2,26,394)</t>
+        </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>1.48x (Net Sales ₹3,34,273 / Spend ₹2,26,394)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2438,17 +2482,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="51" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="51" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2469,25 +2514,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Numeric_Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Subtext</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Full_Card_Display</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Progress_Pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Theme_Color</t>
         </is>
@@ -2501,31 +2551,36 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Total Orders (Active Shopify Orders)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>196 (Active Shopify Orders)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Active Shopify Orders</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Total Orders: 196 (Active Shopify Orders)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
@@ -2539,31 +2594,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Total Revenue (From 196 active orders)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>₹389,789.00 (From 196 active orders)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>389789</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>INR ₹</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>From 196 active orders</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Total Revenue: ₹389,789.00 (From 196 active orders)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2577,31 +2637,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue (169 net orders: 139 delivered + 28 in progress)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+          <t>Net Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>₹334,273.00 (169 net orders: 139 delivered + 28 in progress)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>334273</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>INR ₹</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>169 net orders (139 delivered + 28 in progress)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Net Revenue: ₹334,273.00 (169 net orders)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2615,31 +2680,36 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value (AOV) (Net revenue / 139 successful)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+          <t>Average Order Value (AOV)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>₹2,404.84 (Net revenue / 139 successful)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>2404.841726618705</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>INR ₹</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Net revenue / 139 successful</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>AOV: ₹2,404.84 (Net revenue / 139 successful)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
@@ -2656,15 +2726,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2685,15 +2756,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Numeric_Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Payment_Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Subtext</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Theme_Color</t>
         </is>
@@ -2707,23 +2783,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Full COD Orders (Pre-July 24 100% Cash on Delivery)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+          <t>Full COD Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>52 (Pre-July 24 100% Cash on Delivery)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Full COD</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>52 full COD orders (₹89,768.00)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
@@ -2737,23 +2818,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Partial COD Orders (July 24+ Razorpay Advance Paid)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+          <t>Partial COD Orders</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>23 (July 24+ Razorpay Advance Paid)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Partial COD</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>23 Razorpay Partial COD orders (₹56,777.00)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
@@ -2767,23 +2853,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue (From 40 delivered COD orders)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+          <t>COD Net Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>₹63,090.00 (From 40 delivered COD orders)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>63090</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>From 40 delivered COD orders</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
@@ -2797,23 +2888,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue (From 99 delivered Prepaid orders)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>174562</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>From 99 delivered Prepaid orders</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2827,23 +2923,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value (Prepaid net / 99 successful)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+          <t>Avg Prepaid Order Value</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>₹1,763.25 (Prepaid net / 99 successful)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1763.252525252525</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Prepaid net revenue / 99 successful</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2860,16 +2961,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="59" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="59" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2880,30 +2982,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Primary_Display</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Order_Count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Total_Amount_INR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Stage_Rate_Pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Subtext</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status_Color</t>
         </is>
@@ -2912,29 +3019,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders (139 delivered of 196 total orders)</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
+          <t>Successful Orders</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>139 delivered of 196 total orders</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>237652</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.7091836734693877</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>139 delivered of 196 total orders</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Delivered &amp; self fulfilled</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2943,29 +3055,34 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Doorstep RTO Denied (15 refused of 76 COD orders)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+          <t>Doorstep RTO Denied</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>15 refused of 76 COD orders</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>23478</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.07653061224489796</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Doorstep delivery denials</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2974,29 +3091,34 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Post-Delivery Customer Returns (5 customer returns of 139 delivered)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
+          <t>Post-Delivery Customer Returns</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>5 customer returns of 139 delivered</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>8424</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.03597122302158273</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>5 customer post-delivery returns (out of 139 delivered)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Delivered then sent back</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
@@ -3005,29 +3127,34 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders (7 canceled of 196 total orders)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+          <t>Canceled Orders</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>7 canceled of 196 total orders</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>23614</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>7 canceled of 196 total orders</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Order not accepted</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
@@ -3044,15 +3171,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3063,25 +3191,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Primary_Display</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Order_Count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Total_Amount_INR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Active_Rate_Pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Subtext</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Theme_Color</t>
         </is>
@@ -3090,24 +3223,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress (28 orders awaiting delivery)</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
+          <t>Total In-Progress</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>28 orders awaiting delivery</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>92991</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>28 orders awaiting delivery of 196</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
@@ -3116,24 +3254,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>In Transit (10 orders on the way of 196)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>10 orders on the way of 196</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>29884</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>10 orders on the way of 196</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
@@ -3142,24 +3285,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled (14 orders ready for pickup of 196)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
+          <t>Pickup Scheduled</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>14 orders ready for pickup</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>45520</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>14 orders ready for pickup of 196</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Purple</t>
         </is>
@@ -3168,24 +3316,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled (4 orders pending shipment of 196)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+          <t>Unfulfilled</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4 orders pending shipment</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>17587</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>4 orders pending shipment of 196</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>₹334,273.00 (169 net orders: 139 delivered + 28 in progress)</t>
+          <t>₹334,273.00 (169 net orders: 139 delivered + 32 in progress)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169 net orders (86.2% of total: 139 delivered + 28 in progress)</t>
+          <t>169 net orders (86.2% of total: 139 delivered + 32 in progress)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue: ₹334,273.00 | Subtext: 169 net orders (139 delivered + 28 in progress)</t>
+          <t>Net Revenue: ₹334,273.00 | Subtext: 169 net orders (139 delivered + 32 in progress)</t>
         </is>
       </c>
     </row>
@@ -982,27 +982,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28 (28 orders awaiting delivery)</t>
+          <t>32 (32 orders awaiting delivery)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28 (28 orders awaiting delivery)</t>
+          <t>32 (32 orders awaiting delivery)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28 orders awaiting delivery of 196</t>
+          <t>32 orders awaiting delivery of 196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Count 28 | Total Amount ₹92,991.00 | Active Rate 14.3%</t>
+          <t>Count 32 | Total Amount ₹101,581.00 | Active Rate 16.3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress: 28 | Amount: ₹92,991.00 | Rate: 14.3% | Subtext: 28 orders awaiting delivery</t>
+          <t>Total In-Progress: 32 | Amount: ₹101,581.00 | Rate: 16.3% | Subtext: 32 orders awaiting delivery</t>
         </is>
       </c>
     </row>
@@ -1019,27 +1019,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10 (10 orders on the way of 196)</t>
+          <t>14 (14 orders on the way of 196)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10 (10 orders on the way of 196)</t>
+          <t>14 (14 orders on the way of 196)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10 orders on the way of 196</t>
+          <t>14 orders on the way of 196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Count 10 | Total Amount ₹29,884.00 | Transit Rate 5.1%</t>
+          <t>Count 14 | Total Amount ₹38,474.00 | Transit Rate 7.1%</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>In Transit: 10 | Amount: ₹29,884.00 | Subtext: 10 orders on the way</t>
+          <t>In Transit: 14 | Amount: ₹38,474.00 | Subtext: 14 orders on the way</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>₹334,273.00 (169 net orders: 139 delivered + 28 in progress)</t>
+          <t>₹334,273.00 (169 net orders: 139 delivered + 32 in progress)</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169 net orders (139 delivered + 28 in progress)</t>
+          <t>169 net orders (139 delivered + 32 in progress)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>28 orders awaiting delivery</t>
+          <t>32 orders awaiting delivery</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>92991</v>
+        <v>101581</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>28 orders awaiting delivery of 196</t>
+          <t>32 orders awaiting delivery of 196</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3259,21 +3259,21 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10 orders on the way of 196</t>
+          <t>14 orders on the way of 196</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>29884</v>
+        <v>38474</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.05102040816326531</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>10 orders on the way of 196</t>
+          <t>14 orders on the way of 196</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -480,9 +480,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="64" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="67" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="108" customWidth="1" min="7" max="7"/>
@@ -533,17 +533,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Total Orders</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>196 (Active Shopify Orders)</t>
-        </is>
+          <t>Total Orders: 196 — Active Shopify Store Orders</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>196</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>196 (Active Shopify Orders)</t>
+          <t>196</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,17 +568,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>₹389,789.00 (From 196 active orders)</t>
-        </is>
+          <t>Total Revenue: ₹389,789.00 — From 196 active orders</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>389789</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>₹389,789.00 (From 196 active orders)</t>
+          <t>₹389,789.00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -607,17 +603,15 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>₹334,273.00 (169 net orders: 139 delivered + 32 in progress)</t>
-        </is>
+          <t>Net Revenue: ₹334,273.00 — 169 net orders (139 delivered + 32 in progress)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>334273</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>₹334,273.00 (169 net orders)</t>
+          <t>₹334,273.00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -644,17 +638,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value (AOV)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>₹2,404.84 (Net revenue / 139 successful)</t>
-        </is>
+          <t>Average Order Value: ₹2,404.84 — Net revenue / 139 successful</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2404.841726618705</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>~ ₹2,404.84 (Net revenue / 139 successful)</t>
+          <t>~ ₹2,404.84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -681,17 +673,15 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>₹63,090.00 (From 40 delivered COD orders)</t>
-        </is>
+          <t>COD Net Revenue: ₹63,090.00 — From 40 delivered COD orders</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>63090</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>₹63,090.00 (From 40 delivered COD orders)</t>
+          <t>₹63,090.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -718,17 +708,15 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Avg COD Order Value</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>₹1,577.25 (COD net / 40 successful)</t>
-        </is>
+          <t>Avg COD Order Value: ₹1,577.25 — COD net / 40 successful</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1577.25</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>~ ₹1,577.25 (COD net / 40 successful)</t>
+          <t>~ ₹1,577.25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -755,17 +743,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
-        </is>
+          <t>Prepaid Net Revenue: ₹174,562.00 — From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>174562</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
+          <t>₹174,562.00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -792,17 +778,15 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>₹1,763.25 (Prepaid net / 99 successful)</t>
-        </is>
+          <t>Avg Prepaid Order Value: ₹1,763.25 — Prepaid net / 99 successful</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1763.252525252525</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>~ ₹1,763.25 (Prepaid net / 99 successful)</t>
+          <t>~ ₹1,763.25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -829,17 +813,15 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>139 (139 delivered of 196 total orders)</t>
-        </is>
+          <t>Successful Orders: 139 — 139 delivered of 196 total orders</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>139</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>139 (139 delivered of 196 total orders)</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -866,17 +848,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders (Doorstep RTO)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>15 (15 refused of 76 COD orders)</t>
-        </is>
+          <t>Denied Orders (Doorstep RTO): 15 — 15 refused of 76 COD orders</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15 (15 refused of 76 COD orders)</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -903,17 +883,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Returned Orders</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5 (5 customer returns of 139 delivered)</t>
-        </is>
+          <t>Returned Orders: 5 — 5 customer returns of 139 delivered</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5 (5 customer returns of 139 delivered)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -940,17 +918,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7 (7 canceled of 196 total orders)</t>
-        </is>
+          <t>Canceled Orders: 7 — 7 canceled of 196 total orders</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7 (7 canceled of 196 total orders)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -977,17 +953,15 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress Pipeline</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>32 (32 orders awaiting delivery)</t>
-        </is>
+          <t>Total In-Progress Pipeline: 32 — 32 orders awaiting delivery</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32 (32 orders awaiting delivery)</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1014,17 +988,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>14 (14 orders on the way of 196)</t>
-        </is>
+          <t>In Transit: 14 — 14 orders on the way of 196</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14 (14 orders on the way of 196)</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1051,17 +1023,15 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>14 (14 orders ready for pickup of 196)</t>
-        </is>
+          <t>Pickup Scheduled: 14 — 14 orders ready for pickup of 196</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14 (14 orders ready for pickup of 196)</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1088,17 +1058,15 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>4 (4 orders pending shipment of 196)</t>
-        </is>
+          <t>Unfulfilled: 4 — 4 orders pending shipment of 196</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4 (4 orders pending shipment of 196)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1125,17 +1093,15 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Ad Spend</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>₹2,26,394.41 (Apr 01 - Aug 04)</t>
-        </is>
+          <t>Total Meta Ad Spend: ₹2,26,394.41 — Apr 01 to Aug 04</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>226394.41</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>₹2,26,394.41 (Apr 01 - Aug 04)</t>
+          <t>₹2,26,394.41</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1162,17 +1128,15 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Impressions</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>13.86M (13.86M ad impressions)</t>
-        </is>
+          <t>Total Meta Impressions: 13.86M — 13.86M ad impressions</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>13862586</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13.86M (13.86M ad impressions)</t>
+          <t>13.86M</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1199,17 +1163,15 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Reach</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>13.15M (13.15M unique reach)</t>
-        </is>
+          <t>Total Meta Reach: 13.15M — 13.15M unique reach</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>13156590</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13.15M (13.15M unique reach)</t>
+          <t>13.15M</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1236,17 +1198,15 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cost Per Purchase (CPA)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>₹1,155.07 (Ad spend / 196 conversions)</t>
-        </is>
+          <t>Cost Per Purchase (CPA): ₹1,155.07 — Ad spend / 196 conversions</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1155.07</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>₹1,155.07 (Ad spend / 196 conversions)</t>
+          <t>₹1,155.07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1273,17 +1233,15 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Gross ROAS</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1.72x (Gross Sales ₹3,89,789 / Spend ₹2,26,394)</t>
-        </is>
+          <t>Gross ROAS: 1.72x — Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1.72</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1.72x (Gross Sales ₹3,89,789 / Spend ₹2,26,394)</t>
+          <t>1.72x</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1310,17 +1268,15 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Net ROAS</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1.48x (Net Sales ₹3,34,273 / Spend ₹2,26,394)</t>
-        </is>
+          <t>Net ROAS: 1.48x — Net Sales (₹3,34,273) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1.48</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1.48x (Net Sales ₹3,34,273 / Spend ₹2,26,394)</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -743,287 +743,287 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue: ₹174,562.00 — From 99 delivered Prepaid orders</t>
+          <t>Total Prepaid Orders: 121 — 121 prepaid orders placed (₹243,244.00)</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>174562</v>
+        <v>121</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>₹174,562.00</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>From 99 delivered Prepaid orders</t>
+          <t>121 total prepaid orders (₹243,244.00)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Net delivered prepaid revenue</t>
+          <t>Online Razorpay / Bank Prepaid</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue: ₹174,562.00 | Subtext: From 99 delivered Prepaid orders</t>
+          <t>Total Prepaid Orders: 121 | Subtext: 121 total prepaid orders</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CARD-08</t>
+          <t>CARD-07B</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value: ₹1,763.25 — Prepaid net / 99 successful</t>
+          <t>Prepaid Net Revenue: ₹174,562.00 — From 99 delivered Prepaid orders</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1763.252525252525</v>
+        <v>174562</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>~ ₹1,763.25</t>
+          <t>₹174,562.00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Prepaid net revenue / 99 successful</t>
+          <t>From 99 delivered Prepaid orders</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Average value of 99 delivered Prepaid orders</t>
+          <t>Net delivered prepaid revenue</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Avg Prepaid Order Value: ~ ₹1,763.25 | Subtext: Prepaid net revenue / 99 successful</t>
+          <t>Prepaid Net Revenue: ₹174,562.00 | Subtext: From 99 delivered Prepaid orders</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CARD-09</t>
+          <t>CARD-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders: 139 — 139 delivered of 196 total orders</t>
+          <t>Avg Prepaid Order Value: ₹1,763.25 — Prepaid net / 99 successful</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>139</v>
+        <v>1763.252525252525</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>~ ₹1,763.25</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139 delivered of 196 total orders</t>
+          <t>Prepaid net revenue / 99 successful</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Count 139 | Successful Revenue ₹237,652.00 | Successful Rate 70.9%</t>
+          <t>Average value of 99 delivered Prepaid orders</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Successful Orders: 139 | Revenue: ₹237,652.00 | Rate: 70.9% | Subtext: 139 delivered of 196 total orders</t>
+          <t>Avg Prepaid Order Value: ~ ₹1,763.25 | Subtext: Prepaid net revenue / 99 successful</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CARD-10</t>
+          <t>CARD-09</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders (Doorstep RTO): 15 — 15 refused of 76 COD orders</t>
+          <t>Successful Orders: 139 — 139 delivered of 196 total orders</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15 denied of 196 total orders (19.7% of 76 COD)</t>
+          <t>139 delivered of 196 total orders</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Count 15 | Total Amount ₹23,478.00 | Denied Rate 7.7%</t>
+          <t>Count 139 | Successful Revenue ₹237,652.00 | Successful Rate 70.9%</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders: 15 | Amount: ₹23,478.00 | Rate: 7.7% | Subtext: 15 doorstep delivery refusals</t>
+          <t>Successful Orders: 139 | Revenue: ₹237,652.00 | Rate: 70.9% | Subtext: 139 delivered of 196 total orders</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CARD-11</t>
+          <t>CARD-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Returned Orders: 5 — 5 customer returns of 139 delivered</t>
+          <t>Denied Orders (Doorstep RTO): 15 — 15 refused of 76 COD orders</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5 customer post-delivery returns of 139 delivered</t>
+          <t>15 denied of 196 total orders (19.7% of 76 COD)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Count 5 | Total Refunded ₹8,424.00 | Return Rate 3.6%</t>
+          <t>Count 15 | Total Amount ₹23,478.00 | Denied Rate 7.7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Returned Orders: 5 | Refunded: ₹8,424.00 | Rate: 3.6% | Subtext: 5 customer post-delivery returns</t>
+          <t>Denied Orders: 15 | Amount: ₹23,478.00 | Rate: 7.7% | Subtext: 15 doorstep delivery refusals</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CARD-12</t>
+          <t>CARD-11</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders: 7 — 7 canceled of 196 total orders</t>
+          <t>Returned Orders: 5 — 5 customer returns of 139 delivered</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7 canceled of 196 total orders</t>
+          <t>5 customer post-delivery returns of 139 delivered</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Count 7 | Total Amount ₹23,614.00 | Canceled Rate 3.6%</t>
+          <t>Count 5 | Total Refunded ₹8,424.00 | Return Rate 3.6%</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Canceled Orders: 7 | Amount: ₹23,614.00 | Rate: 3.6% | Subtext: 7 canceled of 196 total orders</t>
+          <t>Returned Orders: 5 | Refunded: ₹8,424.00 | Rate: 3.6% | Subtext: 5 customer post-delivery returns</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CARD-13</t>
+          <t>CARD-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress Pipeline: 32 — 32 orders awaiting delivery</t>
+          <t>Canceled Orders: 7 — 7 canceled of 196 total orders</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32 orders awaiting delivery of 196</t>
+          <t>7 canceled of 196 total orders</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Count 32 | Total Amount ₹101,581.00 | Active Rate 16.3%</t>
+          <t>Count 7 | Total Amount ₹23,614.00 | Canceled Rate 3.6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress: 32 | Amount: ₹101,581.00 | Rate: 16.3% | Subtext: 32 orders awaiting delivery</t>
+          <t>Canceled Orders: 7 | Amount: ₹23,614.00 | Rate: 3.6% | Subtext: 7 canceled of 196 total orders</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CARD-14</t>
+          <t>CARD-13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>In Transit: 14 — 14 orders on the way of 196</t>
+          <t>Total In-Progress Pipeline: 32 — 32 orders awaiting delivery</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14 orders on the way of 196</t>
+          <t>32 orders awaiting delivery of 196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Count 14 | Total Amount ₹38,474.00 | Transit Rate 7.1%</t>
+          <t>Count 32 | Total Amount ₹101,581.00 | Active Rate 16.3%</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>In Transit: 14 | Amount: ₹38,474.00 | Subtext: 14 orders on the way</t>
+          <t>Total In-Progress: 32 | Amount: ₹101,581.00 | Rate: 16.3% | Subtext: 32 orders awaiting delivery</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CARD-15</t>
+          <t>CARD-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled: 14 — 14 orders ready for pickup of 196</t>
+          <t>In Transit: 14 — 14 orders on the way of 196</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1036,260 +1036,295 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14 orders ready for pickup of 196</t>
+          <t>14 orders on the way of 196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Count 14 | Total Amount ₹45,520.00 | Pickup Rate 7.1%</t>
+          <t>Count 14 | Total Amount ₹38,474.00 | Transit Rate 7.1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Pickup Scheduled: 14 | Amount: ₹45,520.00 | Subtext: 14 orders ready for pickup</t>
+          <t>In Transit: 14 | Amount: ₹38,474.00 | Subtext: 14 orders on the way</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CARD-16</t>
+          <t>CARD-15</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled: 4 — 4 orders pending shipment of 196</t>
+          <t>Pickup Scheduled: 14 — 14 orders ready for pickup of 196</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4 orders pending shipment of 196</t>
+          <t>14 orders ready for pickup of 196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Count 4 | Total Amount ₹17,587.00 | Unfulfilled Rate 2.0%</t>
+          <t>Count 14 | Total Amount ₹45,520.00 | Pickup Rate 7.1%</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Unfulfilled: 4 | Amount: ₹17,587.00 | Subtext: 4 orders pending shipment</t>
+          <t>Pickup Scheduled: 14 | Amount: ₹45,520.00 | Subtext: 14 orders ready for pickup</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CARD-17</t>
+          <t>CARD-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Ad Spend: ₹2,26,394.41 — Apr 01 to Aug 04</t>
+          <t>Unfulfilled: 4 — 4 orders pending shipment of 196</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>226394.41</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>₹2,26,394.41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Ads spend (Apr 01 - Aug 04)</t>
+          <t>4 orders pending shipment of 196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Includes Advantage+, Reels, Insta &amp; WA Ads</t>
+          <t>Count 4 | Total Amount ₹17,587.00 | Unfulfilled Rate 2.0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Ad Spend: ₹2,26,394.41 | Subtext: Total Meta Ads spend (Apr 01 - Aug 04)</t>
+          <t>Unfulfilled: 4 | Amount: ₹17,587.00 | Subtext: 4 orders pending shipment</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CARD-18</t>
+          <t>CARD-17</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Impressions: 13.86M — 13.86M ad impressions</t>
+          <t>Total Meta Ad Spend: ₹2,26,394.41 — Apr 01 to Aug 04</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>13862586</v>
+        <v>226394.41</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13.86M</t>
+          <t>₹2,26,394.41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13.86M ad impressions served across Meta</t>
+          <t>Total Meta Ads spend (Apr 01 - Aug 04)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,862,586 total impressions</t>
+          <t>Includes Advantage+, Reels, Insta &amp; WA Ads</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Impressions: 13.86M | Subtext: 13.86M ad impressions served</t>
+          <t>Total Meta Ad Spend: ₹2,26,394.41 | Subtext: Total Meta Ads spend (Apr 01 - Aug 04)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CARD-19</t>
+          <t>CARD-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Reach: 13.15M — 13.15M unique reach</t>
+          <t>Total Meta Impressions: 13.86M — 13.86M ad impressions</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13156590</v>
+        <v>13862586</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13.15M</t>
+          <t>13.86M</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13.15M unique users reached across Meta</t>
+          <t>13.86M ad impressions served across Meta</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,156,590 total unique reach</t>
+          <t>13,862,586 total impressions</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Total Meta Reach: 13.15M | Subtext: 13.15M unique users reached</t>
+          <t>Total Meta Impressions: 13.86M | Subtext: 13.86M ad impressions served</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CARD-20</t>
+          <t>CARD-19</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cost Per Purchase (CPA): ₹1,155.07 — Ad spend / 196 conversions</t>
+          <t>Total Meta Reach: 13.15M — 13.15M unique reach</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1155.07</v>
+        <v>13156590</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>₹1,155.07</t>
+          <t>13.15M</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Ad spend / 196 pixel purchase conversions</t>
+          <t>13.15M unique users reached across Meta</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Average cost to acquire 1 purchase</t>
+          <t>13,156,590 total unique reach</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Cost Per Purchase (CPA): ₹1,155.07 | Subtext: Ad spend / 196 pixel purchase conversions</t>
+          <t>Total Meta Reach: 13.15M | Subtext: 13.15M unique users reached</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CARD-21</t>
+          <t>CARD-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Gross ROAS: 1.72x — Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+          <t>Cost Per Purchase (CPA): ₹1,155.07 — Ad spend / 196 conversions</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.72</v>
+        <v>1155.07</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1.72x</t>
+          <t>₹1,155.07</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+          <t>Ad spend / 196 pixel purchase conversions</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1.72x Gross Return on Ad Spend</t>
+          <t>Average cost to acquire 1 purchase</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Gross ROAS: 1.72x | Subtext: Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+          <t>Cost Per Purchase (CPA): ₹1,155.07 | Subtext: Ad spend / 196 pixel purchase conversions</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>CARD-21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Gross ROAS: 1.72x — Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1.72x</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1.72x Gross Return on Ad Spend</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Gross ROAS: 1.72x | Subtext: Gross Sales (₹3,89,789) / Ad Spend (₹2,26,394)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>CARD-22</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Net ROAS: 1.48x — Net Sales (₹3,34,273) / Ad Spend (₹2,26,394)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C24" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>1.48x</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Net Sales (₹3,34,273) / Ad Spend (₹2,26,394)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1.48x Net Return on Ad Spend</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Net ROAS: 1.48x | Subtext: Net Sales (₹3,34,273) / Ad Spend (₹2,26,394)</t>
         </is>
@@ -2682,16 +2717,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2712,198 +2747,231 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Payment_Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Subtext</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Theme_Color</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Numeric_Value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Payment_Type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Subtext</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Theme_Color</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PAY-01</t>
+          <t>PAY-00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Full COD Orders</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>52 (Pre-July 24 100% Cash on Delivery)</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>52</v>
+          <t>Total Prepaid Orders (121 online prepaid orders)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Full COD</t>
+          <t>121 total prepaid orders (₹243,244.00)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>52 full COD orders (₹89,768.00)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PAY-02</t>
+          <t>PAY-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Partial COD Orders</t>
+          <t>Full COD Orders</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>23 (July 24+ Razorpay Advance Paid)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>23</v>
+          <t>52 (Pre-July 24 100% Cash on Delivery)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Full COD</t>
+        </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Partial COD</t>
+          <t>52 full COD orders (₹89,768.00)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>23 Razorpay Partial COD orders (₹56,777.00)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
           <t>Orange</t>
         </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PAY-03</t>
+          <t>PAY-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>COD Net Revenue</t>
+          <t>Partial COD Orders</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>₹63,090.00 (From 40 delivered COD orders)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>63090</v>
+          <t>23 (July 24+ Razorpay Advance Paid)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Partial COD</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>23 Razorpay Partial COD orders (₹56,777.00)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>From 40 delivered COD orders</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
           <t>Orange</t>
         </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PAY-04</t>
+          <t>PAY-03</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Prepaid Net Revenue</t>
+          <t>COD Net Revenue</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>174562</v>
+          <t>₹63,090.00 (From 40 delivered COD orders)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Prepaid</t>
+          <t>From 40 delivered COD orders</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>From 99 delivered Prepaid orders</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>63090</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>PAY-04</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid Net Revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>₹174,562.00 (From 99 delivered Prepaid orders)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>From 99 delivered Prepaid orders</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>174562</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>PAY-05</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Avg Prepaid Order Value</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>₹1,763.25 (Prepaid net / 99 successful)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Prepaid net revenue / 99 successful</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>1763.252525252525</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Prepaid net revenue / 99 successful</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -20,6 +20,7 @@
     <sheet name="09_Meta_Ads_Category_Perf" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="10_Meta_Ads_Source_Breakdown" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="11_Meta_Ads_Campaign_Details" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="12_Daily_Sales_Trends" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2467,6 +2468,588 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Order_Volume</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Gross_Revenue_INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>10044</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>16476</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>10144</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>21468</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>9805</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>8636</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>6234</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>7068</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4825</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>11059</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>25501</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4776</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>6078</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>8024</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>5738</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>6704</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>14008</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>7248</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>6158</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>5480</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>19070</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>13690</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>6660</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>15850</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>8584</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>39915</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>11840</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>9962</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue: ₹334,273.00 — 169 net orders (139 delivered + 32 in progress)</t>
+          <t>Net Revenue: ₹334,273.00 — 169 net orders (139 delivered + 30 in progress)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169 net orders (86.2% of total: 139 delivered + 32 in progress)</t>
+          <t>169 net orders (86.2% of total: 139 delivered + 30 in progress)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue: ₹334,273.00 | Subtext: 169 net orders (139 delivered + 32 in progress)</t>
+          <t>Net Revenue: ₹334,273.00 | Subtext: 169 net orders (139 delivered + 30 in progress)</t>
         </is>
       </c>
     </row>
@@ -989,30 +989,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress Pipeline: 32 — 32 orders awaiting delivery</t>
+          <t>Total In-Progress Pipeline: 30 — 30 orders awaiting delivery</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32 orders awaiting delivery of 196</t>
+          <t>30 orders awaiting delivery of 196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Count 32 | Total Amount ₹101,581.00 | Active Rate 16.3%</t>
+          <t>Count 30 | Total Amount ₹96,621.00 | Active Rate 15.3%</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Total In-Progress: 32 | Amount: ₹101,581.00 | Rate: 16.3% | Subtext: 32 orders awaiting delivery</t>
+          <t>Total In-Progress: 30 | Amount: ₹96,621.00 | Rate: 15.3% | Subtext: 30 orders awaiting delivery</t>
         </is>
       </c>
     </row>
@@ -1024,30 +1024,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>In Transit: 14 — 14 orders on the way of 196</t>
+          <t>In Transit: 12 — 12 orders on the way of 196</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14 orders on the way of 196</t>
+          <t>12 orders on the way of 196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Count 14 | Total Amount ₹38,474.00 | Transit Rate 7.1%</t>
+          <t>Count 12 | Total Amount ₹33,514.00 | Transit Rate 6.1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>In Transit: 14 | Amount: ₹38,474.00 | Subtext: 14 orders on the way</t>
+          <t>In Transit: 12 | Amount: ₹33,514.00 | Subtext: 12 orders on the way</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>₹334,273.00 (169 net orders: 139 delivered + 32 in progress)</t>
+          <t>₹334,273.00 (169 net orders: 139 delivered + 30 in progress)</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169 net orders (139 delivered + 32 in progress)</t>
+          <t>169 net orders (139 delivered + 30 in progress)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3835,21 +3835,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>32 orders awaiting delivery</t>
+          <t>30 orders awaiting delivery</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>101581</v>
+        <v>96621</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.163265306122449</v>
+        <v>0.1530612244897959</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>32 orders awaiting delivery of 196</t>
+          <t>30 orders awaiting delivery of 196</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3866,21 +3866,21 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14 orders on the way of 196</t>
+          <t>12 orders on the way of 196</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38474</v>
+        <v>33514</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>14 orders on the way of 196</t>
+          <t>12 orders on the way of 196</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -20,7 +20,7 @@
     <sheet name="09_Meta_Ads_Category_Perf" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="10_Meta_Ads_Source_Breakdown" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="11_Meta_Ads_Campaign_Details" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="12_Daily_Sales_Trends" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="13_Daily_Meta_Ads_Spend" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2474,12 +2474,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2490,559 +2492,2417 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Daily_Order_Volume</t>
+          <t>Daily_Meta_Ad_Spend_INR</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Daily_Gross_Revenue_INR</t>
+          <t>Daily_Impressions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Reach</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Pixel_Purchases</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1112</v>
+        <v>1167.62</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>159221</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>147954</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>10044</v>
+        <v>944.66</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>137398</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>133069</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>7980</v>
+        <v>1262.75</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>192414</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>188036</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>16476</v>
+        <v>1244.69</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>189833</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>180652</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1290</v>
+        <v>977.1799999999999</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>151425</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>145614</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>10144</v>
+        <v>1072.28</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>187291</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>187236</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>6040</v>
+        <v>1013.19</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>174668</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>172876</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>3534</v>
+        <v>956.47</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>152656</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>145556</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>21468</v>
+        <v>968.77</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>136073</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>130162</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>9805</v>
+        <v>960.75</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>134394</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>125039</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>8636</v>
+        <v>1034.57</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>120027</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>113818</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>6234</v>
+        <v>993.3200000000001</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>100867</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>93812</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>5022</v>
+        <v>1022.46</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>111069</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>104831</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>7068</v>
+        <v>979.01</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>108833</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>99417</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>4825</v>
+        <v>1066.6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>84960</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>74430</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>11059</v>
+        <v>217.31</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>38528</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>38528</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>25501</v>
+        <v>175</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>33222</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>31054</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>4776</v>
+        <v>207.03</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>29241</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>27871</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>6078</v>
+        <v>194.49</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>34198</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>32318</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>8024</v>
+        <v>202.08</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>35434</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>33673</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>1032</v>
+        <v>201.02</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>37544</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>35492</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>5738</v>
+        <v>194.96</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>46539</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>43373</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>6704</v>
+        <v>191.39</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>40532</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>37888</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>10538</v>
+        <v>209.48</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>42198</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>39504</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>3256</v>
+        <v>204.56</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>42899</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>39691</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>14008</v>
+        <v>196.93</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>44883</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>39407</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>7248</v>
+        <v>197</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>44208</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>40396</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>6158</v>
+        <v>188.24</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>36524</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>33884</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>4170</v>
+        <v>190.27</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>37544</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>35564</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>5460</v>
+        <v>293.51</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>60998</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>59430</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>4960</v>
+        <v>674.26</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>130669</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>121169</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>5480</v>
+        <v>707.36</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>165041</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>150351</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>19070</v>
+        <v>844.3599999999999</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>340711</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>330494</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>13690</v>
+        <v>537.9200000000001</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>123008</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>112644</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>6660</v>
+        <v>598.76</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>128132</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>121741</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>6550</v>
+        <v>17.45</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>4287</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>15850</v>
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>7800</v>
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>8584</v>
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>39915</v>
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>11840</v>
+        <v>214.45</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>65227</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>64423</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>247.21</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>45532</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>41954</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>818.0899999999999</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>91501</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>85881</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1010.92</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>104454</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>91215</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1019.97</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>91586</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>82059</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>830.74</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>128833</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>123142</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>784.8199999999999</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>87349</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>78283</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>769.75</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>71027</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>63724</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>833.8800000000001</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>75173</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>68153</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>998.3299999999999</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>280893</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>273353</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>950.6600000000001</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>106303</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>97404</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1341.36</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>166698</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>156044</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1233.31</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>146121</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>138929</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1093.93</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>130229</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>124375</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1208.12</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>169959</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>159414</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1244.55</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>186391</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>175674</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1387.67</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>184850</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>176503</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>1068.48</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>147218</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>138521</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>1085.45</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>134709</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>125073</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>1392.85</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>145992</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>134582</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>801.48</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>89146</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>83603</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>1376.14</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>164696</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>149323</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>1113.44</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>155624</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>145187</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>1140.34</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>152346</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>145047</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>1132.56</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>124016</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>117591</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>1106.83</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>129781</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>126564</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>1013.36</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>89729</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>86832</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>1011.09</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>92146</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>89488</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>1248.23</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>125435</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>119265</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>1033.66</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>101544</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>96283</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>1135.13</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>109986</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>102732</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>1087.78</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>101813</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>96736</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>1259.9</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>131564</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>128281</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>1178.26</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>111254</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>107443</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>953.3199999999999</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>92242</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>89727</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1289.84</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>167898</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>160149</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>1088.65</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>124560</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>123003</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>1142.68</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>97096</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>94827</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>1342.54</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>103489</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>99942</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>1343.2</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>88692</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>86453</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>1092.21</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>82609</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>80995</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>1291.11</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>76255</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>75550</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>1526.93</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>94415</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>91609</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>1699.56</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>81631</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>78423</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>1017.52</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>25339</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>24164</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>2864.14</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>106921</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>103072</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>121.13</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>4399</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>4219</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>3424.21</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>136298</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>127605</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>20835</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>20345</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>2331.12</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>82745</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>1658.34</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>57706</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>55086</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>1513.13</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>90394</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>88635</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>3203.27</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>157964</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>147634</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>3322.77</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>150155</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>143785</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>3042.28</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>144118</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>138473</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>2400.14</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>121782</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>118434</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>2504.42</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>123796</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>118722</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>2503.89</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>118671</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>114126</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>2487.76</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>127272</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>123818</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>2731.01</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>122955</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>119297</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>4671.88</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>125570</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>119959</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>3708.62</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>114921</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>111248</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>4608.98</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>142747</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>134409</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4558.690000000001</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>139141</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>130968</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>139413</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>130794</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>3909.8</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>127317</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>123203</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>3752.14</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>124333</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>120671</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>4923.72</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>136227</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>129975</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>4425.94</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>126165</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>117759</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>5251.19</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>156145</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>148153</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>4366.8</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>153270</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>146610</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>4573.360000000001</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>150778</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>144470</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>4265.29</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>140938</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>134815</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>137965</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>135234</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>4112.01</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>108516</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>104715</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>3800.35</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>105020</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>99787</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>5330.68</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>125394</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>116708</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>4916.950000000001</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>141165</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>135313</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>4461.23</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>157110</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>146371</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>3976.47</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>129307</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>121770</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>4238.28</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>94619</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>5226.67</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>103409</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>97468</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>5685.67</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>197980</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>181513</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>7407.9</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>179592</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>166065</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>6790.78</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>93142</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>83378</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>12152</v>
+      <c r="B127" s="5" t="n">
+        <v>2814.07</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>27850</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>25474</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -21,6 +21,9 @@
     <sheet name="10_Meta_Ads_Source_Breakdown" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="11_Meta_Ads_Campaign_Details" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="13_Daily_Meta_Ads_Spend" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14_Acquisition_Day_Wise" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15_Acquisition_Week_Wise" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16_Acquisition_Month_Wise" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4910,6 +4913,4690 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H127"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date_Str</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Orders</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Unique_Customers</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Daily_Gross_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ad_Pixel_Conversions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CPA_Ad_Conversions_INR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CPA_Total_Orders_INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1167.62</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>944.66</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1262.75</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1244.69</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>977.1799999999999</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1072.28</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1013.19</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>956.47</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>968.77</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>960.75</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1034.57</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>993.3200000000001</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1022.46</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>979.01</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1066.6</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>217.31</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>207.03</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>194.49</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>202.08</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>201.02</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>194.96</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>191.39</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>209.48</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>204.56</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>196.93</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>190.27</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>293.51</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>674.26</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>707.36</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>844.3599999999999</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>537.9200000000001</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>598.76</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>214.45</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>247.21</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>818.0899999999999</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>1010.92</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>1019.97</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>830.74</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>784.8199999999999</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>769.75</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>833.8800000000001</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>998.3299999999999</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>950.6600000000001</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>1341.36</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>1233.31</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>1093.93</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>1208.12</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>1244.55</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>1387.67</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>1068.48</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>1085.45</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>1392.85</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>801.48</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>1376.14</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>1113.44</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>1140.34</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>1132.56</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>1106.83</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>1013.36</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>1011.09</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>1248.23</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>1033.66</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>1135.13</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>1087.78</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1259.9</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>1178.26</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>953.3199999999999</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>1289.84</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1088.65</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>1142.68</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1342.54</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1343.2</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>1092.21</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1291.11</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1291.11</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>1526.93</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>763.465</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>1526.93</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>1699.56</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>849.7800000000001</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>10044</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>1017.52</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>203.504</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>169.5866666666667</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>2864.14</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>409.1628571428571</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>409.1628571428571</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>121.13</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>16476</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>3424.21</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>311.2918181818182</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>285.3508333333334</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1290</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>595.28</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>10144</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>2331.12</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>388.52</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>6040</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>1658.34</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>414.585</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>414.585</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>3534</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1513.13</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>504.3766666666667</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>504.3766666666667</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>21468</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>3203.27</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>266.9391666666667</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>266.9391666666667</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>9805</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>3322.77</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>553.795</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>553.795</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>8636</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>3042.28</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>608.456</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>507.0466666666667</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>6234</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>2400.14</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>600.035</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>800.0466666666666</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>5022</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>2504.42</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>626.105</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>626.105</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>2503.89</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>625.9725</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>500.778</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>4825</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>2487.76</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>829.2533333333334</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>829.2533333333334</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>11059</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>2731.01</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>390.1442857142857</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>390.1442857142857</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>25501</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>4671.88</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>467.188</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>467.188</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>4776</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>3708.62</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>1236.206666666667</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>1236.206666666667</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>6078</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>4608.98</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>921.796</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>921.796</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>8024</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>4558.690000000001</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1139.6725</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1139.6725</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1032</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>5738</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>3909.8</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>1303.266666666667</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>1303.266666666667</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>6704</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>3752.14</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>3752.14</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>1876.07</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>10538</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>4923.72</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>984.744</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>984.744</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>3256</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>4425.94</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>4425.94</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>2212.97</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>14008</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>5251.19</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>875.1983333333333</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>875.1983333333333</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>7248</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>4366.8</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>1455.6</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>1091.7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>6158</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>4573.360000000001</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>914.6720000000001</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>914.6720000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>4170</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>4265.29</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>1421.763333333333</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>1421.763333333333</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>5460</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1081.625</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>1081.625</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>4960</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>4112.01</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>2056.005</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>2056.005</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>5480</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>3800.35</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>1900.175</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>1900.175</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>19070</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>5330.68</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>761.5257142857143</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>666.335</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>13690</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>4916.950000000001</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>702.4214285714287</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>819.4916666666668</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>6660</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>4461.23</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>1487.076666666667</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>1487.076666666667</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>6550</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>3976.47</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1325.49</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>994.1175000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>15850</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>4238.28</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>847.6559999999999</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>847.6559999999999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>5226.67</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>1306.6675</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>1306.6675</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>8584</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>5685.67</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>5685.67</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>2842.835</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>39915</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>7407.9</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>673.4454545454545</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>673.4454545454545</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>11840</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>6790.78</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>848.8475</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>1697.695</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>12152</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>2814.07</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>1407.035</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>938.0233333333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year_Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Week_Start_Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Week_End_Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Active_Days_In_Week</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Orders</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Unique_Customers</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Gross_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Pixel_Conversions</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_CPA_Per_Order_INR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Orders_Per_Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>5596.9</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>6999.35</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3861.9</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1400.42</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3095</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4926.2</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>7221.22</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>8188.6</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>7893.76</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7896.28</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>8590.23</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-W26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>36902</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11248.77</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>416.6211111111111</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>3.857142857142857</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-W27</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>65861</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>17471.05</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>436.77625</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-W28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>64329</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>23216.56</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>627.4745945945946</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.285714285714286</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-W29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>49300</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>31341.03</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1362.653478260869</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.285714285714286</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-W30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>52546</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>30774.99</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1099.106785714286</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-W31</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>99049</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>35913.17</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1026.090571428571</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-W32</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>23992</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>9604.85</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>1372.121428571429</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year_Month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Active_Days_In_Month</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Orders</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Unique_Customers</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Gross_Revenue_INR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Pixel_Conversions</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_CPA_Per_Order_INR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Orders_Per_Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>18727.59</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>23716.13</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>53086</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>39618.5</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1070.77027027027</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.233333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>266402</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>121633.77</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>868.8126428571429</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.516129032258065</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>72491</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>22698.42</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1134.921</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -24,6 +24,9 @@
     <sheet name="14_Acquisition_Day_Wise" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="15_Acquisition_Week_Wise" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="16_Acquisition_Month_Wise" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17_Meta_Ads_Day_Acquisition" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="18_Meta_Ads_Week_Acquisition" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="19_Meta_Ads_Month_Acquisition" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9597,6 +9600,4016 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G127"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date_Str</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ads_Driven_Orders</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ads_Impressions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ads_Unique_Customers_Reached</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ads_CPA_INR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ads_Orders_Per_Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1167.62</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>159221</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>147954</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>944.66</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>137398</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>133069</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1262.75</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>192414</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>188036</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1244.69</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>189833</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>180652</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>977.1799999999999</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>151425</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>145614</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1072.28</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>187291</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>187236</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1013.19</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>174668</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>172876</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>956.47</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>152656</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>145556</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>968.77</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>136073</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>130162</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>960.75</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>134394</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>125039</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1034.57</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>120027</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>113818</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>993.3200000000001</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>100867</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>93812</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1022.46</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>111069</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>104831</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>979.01</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>108833</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>99417</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1066.6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>84960</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>74430</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>217.31</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>38528</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>38528</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>33222</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>31054</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>207.03</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>29241</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>27871</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>194.49</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>34198</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>32318</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>202.08</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>35434</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>33673</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>201.02</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>37544</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>35492</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>194.96</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>46539</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>43373</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>191.39</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>40532</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>37888</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>209.48</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>42198</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>39504</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>204.56</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>42899</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>39691</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>196.93</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>44883</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>39407</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>44208</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>40396</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>36524</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>33884</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>190.27</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>37544</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>35564</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>293.51</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>60998</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>59430</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>674.26</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>130669</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>121169</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>707.36</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>165041</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>150351</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>844.3599999999999</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>340711</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>330494</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>537.9200000000001</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>123008</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>112644</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>598.76</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>128132</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>121741</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>4287</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>214.45</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>65227</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>64423</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>247.21</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>45532</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>41954</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>818.0899999999999</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>91501</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>85881</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1010.92</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>104454</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>91215</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1019.97</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>91586</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>82059</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>830.74</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>128833</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>123142</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>784.8199999999999</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>87349</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>78283</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>769.75</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>71027</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>63724</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>833.8800000000001</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>75173</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>68153</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>998.3299999999999</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>280893</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>273353</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>950.6600000000001</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>106303</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>97404</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1341.36</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>166698</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>156044</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1233.31</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>146121</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>138929</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1093.93</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>130229</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>124375</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1208.12</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>169959</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>159414</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1244.55</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>186391</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>175674</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1387.67</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>184850</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>176503</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>1068.48</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>147218</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>138521</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>1085.45</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>134709</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>125073</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>1392.85</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>145992</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>134582</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>801.48</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>89146</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>83603</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>1376.14</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>164696</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>149323</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>1113.44</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>155624</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>145187</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>1140.34</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>152346</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>145047</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>1132.56</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>124016</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>117591</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>1106.83</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>129781</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>126564</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>1013.36</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>89729</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>86832</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>1011.09</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>92146</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>89488</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>1248.23</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>125435</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>119265</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>1033.66</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>101544</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>96283</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>1135.13</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>109986</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>102732</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>1087.78</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>101813</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>96736</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>1259.9</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>131564</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>128281</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>1178.26</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>111254</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>107443</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>953.3199999999999</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>92242</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>89727</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1289.84</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>167898</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>160149</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>1088.65</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>124560</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>123003</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>1142.68</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>97096</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>94827</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>1342.54</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>103489</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>99942</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>1343.2</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>88692</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>86453</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>1092.21</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>82609</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>80995</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>1291.11</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>76255</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>75550</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>1291.11</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>1526.93</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>94415</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>91609</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>763.465</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>1699.56</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>81631</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>78423</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>849.7800000000001</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>1017.52</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>25339</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>24164</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>203.504</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>2864.14</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>106921</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>103072</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>409.1628571428571</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>121.13</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>4399</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>4219</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>3424.21</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>136298</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>127605</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>311.2918181818182</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>20835</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>20345</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>595.28</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>2331.12</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>86984</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>82745</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>1658.34</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>57706</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>55086</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>414.585</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>1513.13</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>90394</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>88635</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>504.3766666666667</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>3203.27</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>157964</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>147634</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>266.9391666666667</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>3322.77</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>150155</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>143785</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>553.795</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>3042.28</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>144118</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>138473</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>608.456</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>2400.14</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>121782</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>118434</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>600.035</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>2504.42</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>123796</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>118722</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>626.105</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>2503.89</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>118671</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>114126</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>625.9725</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>2487.76</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>127272</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>123818</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>829.2533333333334</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>2731.01</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>122955</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>119297</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>390.1442857142857</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>4671.88</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>125570</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>119959</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>467.188</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>3708.62</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>114921</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>111248</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>1236.206666666667</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>4608.98</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>142747</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>134409</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>921.796</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4558.690000000001</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>139141</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>130968</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>1139.6725</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>139413</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>130794</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>4519.55</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>3909.8</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>127317</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>123203</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>1303.266666666667</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>3752.14</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>124333</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>120671</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>3752.14</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>4923.72</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>136227</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>129975</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>984.744</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>4425.94</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>126165</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>117759</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>4425.94</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>5251.19</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>156145</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>148153</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>875.1983333333333</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>4366.8</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>153270</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>146610</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>1455.6</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>4573.360000000001</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>150778</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>144470</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>914.6720000000001</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>4265.29</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>140938</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>134815</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>1421.763333333333</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>137965</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>135234</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>1081.625</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>4112.01</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>108516</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>104715</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>2056.005</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>3800.35</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>105020</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>99787</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>1900.175</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>5330.68</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>125394</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>116708</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>761.5257142857143</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>4916.950000000001</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>141165</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>135313</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>702.4214285714287</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>4461.23</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>157110</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>146371</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>1487.076666666667</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>3976.47</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>129307</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>121770</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>1325.49</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>4238.28</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>94619</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>847.6559999999999</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>5226.67</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>103409</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>97468</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>1306.6675</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>5685.67</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>197980</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>181513</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>5685.67</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>7407.9</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>179592</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>166065</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>673.4454545454545</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>6790.78</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>93142</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>83378</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>848.8475</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>2814.07</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>27850</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>25474</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>1407.035</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year_Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Week_Start_Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Week_End_Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Active_Days_In_Week</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ads_Driven_Orders</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ads_Unique_Customers_Reached</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ads_Impressions</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ads_CPA_INR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly_Ads_Orders_Per_Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>5596.9</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>795325</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>830291</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>6999.35</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>968499</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1005976</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3861.9</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>408449</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>440051</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1400.42</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>269028</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>290029</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3095</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>771288</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>815695</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>238633</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>255427</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4926.2</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>566957</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>614482</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7221.22</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>921982</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>976444</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8188.6</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>993370</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1058265</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7893.76</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>860032</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>908338</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7896.28</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>740467</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>773838</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8590.23</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>720919</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>740599</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>8590.23</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-W26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>11248.77</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>449437</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>469838</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>401.7417857142858</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-W27</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>17471.05</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>774792</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>809103</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>436.77625</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-W28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>23216.56</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>841579</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>875932</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>644.9044444444445</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>5.142857142857143</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-W29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>31341.03</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>901523</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>948741</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1492.43</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-W30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>30774.99</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>882339</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>921881</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1183.653461538462</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>3.714285714285714</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-W31</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>35913.17</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>943119</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1006664</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1056.269705882353</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>4.857142857142857</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-W32</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>9604.85</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>108852</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>120992</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>960.485</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9834,6 +13847,212 @@
         <is>
           <t>Blue</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year_Month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Active_Days_In_Month</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ad_Spend_INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ads_Driven_Orders</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ads_Unique_Customers_Reached</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ads_Impressions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ads_CPA_INR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly_Ads_Orders_Per_Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>18727.59</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>2610575</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2745621</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>23716.13</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>3322956</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3541039</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>39618.5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2908686</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3037303</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1015.858974358974</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>121633.77</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>3857943</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4040059</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>900.9908888888889</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.354838709677419</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>22698.42</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>456430</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>498564</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1031.746363636364</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -9621,7 +9621,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Date_Str</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -609,20 +609,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue: ₹340,033.00 — 171 net orders (142 delivered + 28 in progress)</t>
+          <t>Net Revenue: ₹336,463.00 — 170 net orders (142 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>340033</v>
+        <v>336463</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>₹340,033.00</t>
+          <t>₹336,463.00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171 net orders (86.2% of total: 142 delivered + 28 in progress)</t>
+          <t>170 net orders (86.2% of total: 142 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue: ₹340,033.00 | Subtext: 171 net orders (142 delivered + 28 in progress)</t>
+          <t>Net Revenue: ₹336,463.00 | Subtext: 170 net orders (142 delivered + 28 in progress)</t>
         </is>
       </c>
     </row>
@@ -644,15 +644,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value: ₹2,394.60 — Net revenue / 142 successful</t>
+          <t>Average Order Value: ₹2,369.46 — Net revenue / 142 successful</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2394.598591549296</v>
+        <v>2369.457746478873</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>~ ₹2,394.60</t>
+          <t>~ ₹2,369.46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value: ~ ₹2,394.60 | Subtext: Net revenue / 142 successful</t>
+          <t>Average Order Value: ~ ₹2,369.46 | Subtext: Net revenue / 142 successful</t>
         </is>
       </c>
     </row>
@@ -889,30 +889,30 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders (Doorstep RTO): 14 — 14 refused of 76 COD orders</t>
+          <t>Denied Orders (Doorstep RTO): 15 — 15 refused of 76 COD orders</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14 denied of 197 total orders (19.7% of 76 COD)</t>
+          <t>15 denied of 197 total orders (19.7% of 76 COD)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Count 14 | Total Amount ₹19,908.00 | Denied Rate 7.1%</t>
+          <t>Count 15 | Total Amount ₹23,478.00 | Denied Rate 7.6%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Denied Orders: 14 | Amount: ₹19,908.00 | Rate: 7.1% | Subtext: 14 doorstep delivery refusals</t>
+          <t>Denied Orders: 15 | Amount: ₹23,478.00 | Rate: 7.6% | Subtext: 15 doorstep delivery refusals</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.8888848573449506</v>
+        <v>0.8795524721331579</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Net sales (₹340,033) / Total Ad Spend (₹382,539)</t>
+          <t>Net sales (₹336,463) / Total Ad Spend (₹382,539)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -61231,7 +61231,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="64" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="51" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
@@ -61385,11 +61385,11 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>₹340,033.00 (171 net orders: 142 delivered + 28 in progress)</t>
+          <t>₹336,463.00 (170 net orders: 142 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>340033</v>
+        <v>336463</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -61398,12 +61398,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171 net orders (142 delivered + 28 in progress)</t>
+          <t>170 net orders (142 delivered + 28 in progress)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Net Revenue: ₹340,033.00 (171 net orders)</t>
+          <t>Net Revenue: ₹336,463.00 (170 net orders)</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -61428,11 +61428,11 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>₹2,394.60 (Net revenue / 142 successful)</t>
+          <t>₹2,369.46 (Net revenue / 142 successful)</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2394.598591549296</v>
+        <v>2369.457746478873</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>AOV: ₹2,394.60 (Net revenue / 142 successful)</t>
+          <t>AOV: ₹2,369.46 (Net revenue / 142 successful)</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
@@ -61836,21 +61836,21 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14 refused of 76 COD orders</t>
+          <t>15 refused of 76 COD orders</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19908</v>
+        <v>23478</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.07106598984771574</v>
+        <v>0.07614213197969544</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>14 doorstep delivery refusals (out of 76 COD orders)</t>
+          <t>15 doorstep delivery refusals (out of 76 COD orders)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>269684.5</v>
+        <v>269900.69</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Meta (₹232,066) + Google (₹37,618)</t>
+          <t>Meta (₹232,066) + Google (₹37,834)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>37618.12</v>
+        <v>37834.31</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>214.0353174603175</v>
+        <v>213.5290268987342</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>35.45534401508011</v>
+        <v>35.53</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.453472483587303</v>
+        <v>1.452308254565781</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Gross sales (₹391,979) / Total Ad Spend (₹269,684)</t>
+          <t>Gross sales (₹391,979) / Total Ad Spend (₹269,901)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.247617122971472</v>
+        <v>1.246617783748533</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Net sales (₹336,463) / Total Ad Spend (₹269,684)</t>
+          <t>Net sales (₹336,463) / Total Ad Spend (₹269,901)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">

--- a/Janvi_4see_Magic_Dashboard_Master.xlsx
+++ b/Janvi_4see_Magic_Dashboard_Master.xlsx
@@ -55025,12 +55025,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -55051,22 +55051,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Numeric_Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Payment_Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Subtext</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Theme_Color</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Numeric_Value</t>
         </is>
       </c>
     </row>
@@ -55078,29 +55078,29 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Total Prepaid Orders (121 online prepaid orders)</t>
+          <t>Total Prepaid Orders</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>121 total prepaid orders (₹252,754.00)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -55114,28 +55114,26 @@
           <t>Full COD Orders</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>52 (Pre-July 24 100% Cash on Delivery)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Full COD</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>52 full COD orders (₹89,768.00)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -55149,28 +55147,26 @@
           <t>Partial COD Orders</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>26 (July 24+ Razorpay Advance Paid)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Partial COD</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23 Razorpay Partial COD orders (₹63,037.00)</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>24 Razorpay Partial COD orders (₹63,037.00)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Orange</t>
         </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -55184,28 +55180,26 @@
           <t>COD Net Revenue</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>₹71,130.00 (From 44 delivered COD orders)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>71130</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>71130</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>From 44 delivered COD orders</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>71130</v>
       </c>
     </row>
     <row r="6">
@@ -55219,28 +55213,26 @@
           <t>Prepaid Net Revenue</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>₹183,422.00 (From 102 delivered Prepaid orders)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>183422</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>183422</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>From 102 delivered Prepaid orders</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>183422</v>
       </c>
     </row>
     <row r="7">
@@ -55254,28 +55246,26 @@
           <t>Avg Prepaid Order Value</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>₹1,798.25 (Prepaid net / 102 successful)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>1798.254901960784</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1798.254901960784</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Prepaid net revenue / 102 successful</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1798.254901960784</v>
       </c>
     </row>
   </sheetData>
